--- a/Workflows/01_Define_Metric/suspOpt_sweep_param_limits_results.xlsx
+++ b/Workflows/01_Define_Metric/suspOpt_sweep_param_limits_results.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="libxl" lastEdited="7" lowestEdited="7" rupBuild="4.6.0"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -503,7 +503,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2948" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3364" uniqueCount="195">
   <si>
     <t>Label</t>
   </si>
@@ -1900,31 +1900,31 @@
         <v>0.15</v>
       </c>
       <c r="F2" s="3">
-        <v>0.14124394581464875</v>
+        <v>0.1412400136081283</v>
       </c>
       <c r="G2" s="3">
-        <v>0.14039488575211237</v>
+        <v>0.14037997917856626</v>
       </c>
       <c r="H2" s="2">
-        <v>0.00084906006253637756</v>
+        <v>0.00086003442956203435</v>
       </c>
       <c r="I2" s="4">
-        <v>27.517604798762079</v>
+        <v>27.517608701902816</v>
       </c>
       <c r="J2" s="4">
-        <v>27.507452115879005</v>
+        <v>27.507351511964941</v>
       </c>
       <c r="K2" s="2">
-        <v>0.010152682883074249</v>
+        <v>0.0102571899378745</v>
       </c>
       <c r="L2" s="4">
-        <v>1.0278560409092758</v>
+        <v>1.0278569552403256</v>
       </c>
       <c r="M2" s="4">
-        <v>1.0267828714407627</v>
+        <v>1.026754978174051</v>
       </c>
       <c r="N2" s="2">
-        <v>0.0010731694685131021</v>
+        <v>0.0011019770662745731</v>
       </c>
       <c r="O2" s="8" t="b">
         <v>1</v>
@@ -1985,31 +1985,31 @@
         <v>0.501</v>
       </c>
       <c r="F3" s="3">
-        <v>0.14117826830669333</v>
+        <v>0.14118387589502618</v>
       </c>
       <c r="G3" s="3">
-        <v>0.14005848898472176</v>
+        <v>0.14004273211528412</v>
       </c>
       <c r="H3" s="2">
-        <v>0.0011197793219715757</v>
+        <v>0.0011411437797420598</v>
       </c>
       <c r="I3" s="4">
-        <v>27.522496900682484</v>
+        <v>27.522464385968135</v>
       </c>
       <c r="J3" s="4">
-        <v>27.493323904433339</v>
+        <v>27.492023526332616</v>
       </c>
       <c r="K3" s="2">
-        <v>0.029172996249144489</v>
+        <v>0.030440859635518791</v>
       </c>
       <c r="L3" s="4">
-        <v>1.0296906842357796</v>
+        <v>1.0301648242071213</v>
       </c>
       <c r="M3" s="4">
-        <v>1.0242471002521836</v>
+        <v>1.0242499729441768</v>
       </c>
       <c r="N3" s="2">
-        <v>0.005443583983596012</v>
+        <v>0.0059148512629445538</v>
       </c>
       <c r="O3" s="8" t="b">
         <v>1</v>
@@ -2070,31 +2070,31 @@
         <v>0.47999999999999998</v>
       </c>
       <c r="F4" s="3">
-        <v>0.13557569893261873</v>
+        <v>0.13556222215467947</v>
       </c>
       <c r="G4" s="3">
-        <v>0.14376922353350727</v>
+        <v>0.14377064521916952</v>
       </c>
       <c r="H4" s="2">
-        <v>0.008193524600888541</v>
+        <v>0.0082084230644900447</v>
       </c>
       <c r="I4" s="4">
-        <v>27.450966522901297</v>
+        <v>27.449014793931269</v>
       </c>
       <c r="J4" s="4">
-        <v>27.546599167395016</v>
+        <v>27.546707641864884</v>
       </c>
       <c r="K4" s="2">
-        <v>0.095632644493718999</v>
+        <v>0.097692847933615212</v>
       </c>
       <c r="L4" s="4">
-        <v>1.023608643294686</v>
+        <v>1.0235000180304801</v>
       </c>
       <c r="M4" s="4">
-        <v>1.0330391985309224</v>
+        <v>1.0323302064618214</v>
       </c>
       <c r="N4" s="2">
-        <v>0.0094305552362363709</v>
+        <v>0.0088301884313413126</v>
       </c>
       <c r="O4" s="8" t="b">
         <v>1</v>
@@ -2148,31 +2148,31 @@
         <v>-0.055</v>
       </c>
       <c r="F5" s="3">
-        <v>0.14124702395774258</v>
+        <v>0.1412511022338446</v>
       </c>
       <c r="G5" s="3">
-        <v>0.13986950725431982</v>
+        <v>0.13987014952909208</v>
       </c>
       <c r="H5" s="2">
-        <v>0.0013775167034227598</v>
+        <v>0.001380952704752525</v>
       </c>
       <c r="I5" s="4">
-        <v>27.511398311569735</v>
+        <v>27.511429678134334</v>
       </c>
       <c r="J5" s="4">
-        <v>27.511960773782789</v>
+        <v>27.51134533589692</v>
       </c>
       <c r="K5" s="2">
-        <v>0.00056246221305400468</v>
+        <v>8.4342237414603005e-05</v>
       </c>
       <c r="L5" s="4">
-        <v>1.0275782890349494</v>
+        <v>1.0273318278830801</v>
       </c>
       <c r="M5" s="4">
-        <v>1.0272543407810495</v>
+        <v>1.0273488247747815</v>
       </c>
       <c r="N5" s="2">
-        <v>0.00032394825389991944</v>
+        <v>1.6996891701426264e-05</v>
       </c>
       <c r="O5" s="8" t="b">
         <v>1</v>
@@ -2226,31 +2226,31 @@
         <v>0.501</v>
       </c>
       <c r="F6" s="3">
-        <v>0.14217618195001083</v>
+        <v>0.14216989004980291</v>
       </c>
       <c r="G6" s="3">
-        <v>0.13869901471527335</v>
+        <v>0.13871140983069224</v>
       </c>
       <c r="H6" s="2">
-        <v>0.0034771672347374827</v>
+        <v>0.0034584802191106601</v>
       </c>
       <c r="I6" s="4">
-        <v>27.50770742048968</v>
+        <v>27.508336482710831</v>
       </c>
       <c r="J6" s="4">
-        <v>27.513491356133329</v>
+        <v>27.51382878540096</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0057839356436488742</v>
+        <v>0.005492302690129236</v>
       </c>
       <c r="L6" s="4">
-        <v>1.0279056747422415</v>
+        <v>1.0272735386367267</v>
       </c>
       <c r="M6" s="4">
-        <v>1.0266851880191552</v>
+        <v>1.02628431046573</v>
       </c>
       <c r="N6" s="2">
-        <v>0.0012204867230862781</v>
+        <v>0.00098922817099666993</v>
       </c>
       <c r="O6" s="8" t="b">
         <v>1</v>
@@ -2304,31 +2304,31 @@
         <v>0.46000000000000002</v>
       </c>
       <c r="F7" s="3">
-        <v>0.1337609737506385</v>
+        <v>0.13378668598874247</v>
       </c>
       <c r="G7" s="3">
-        <v>0.14656012768503574</v>
+        <v>0.14654645497234098</v>
       </c>
       <c r="H7" s="2">
-        <v>0.012799153934397234</v>
+        <v>0.012759768983598513</v>
       </c>
       <c r="I7" s="4">
-        <v>27.516125462069738</v>
+        <v>27.516124895578173</v>
       </c>
       <c r="J7" s="4">
-        <v>27.498019416017826</v>
+        <v>27.499049606350127</v>
       </c>
       <c r="K7" s="2">
-        <v>0.018106046051912017</v>
+        <v>0.017075289228046131</v>
       </c>
       <c r="L7" s="4">
-        <v>1.0261053928073032</v>
+        <v>1.0271531630635944</v>
       </c>
       <c r="M7" s="4">
-        <v>1.032106693759953</v>
+        <v>1.0321278402135088</v>
       </c>
       <c r="N7" s="2">
-        <v>0.0060013009526498351</v>
+        <v>0.0049746771499143971</v>
       </c>
       <c r="O7" s="8" t="b">
         <v>1</v>
@@ -2382,31 +2382,31 @@
         <v>0.01</v>
       </c>
       <c r="F8" s="3">
-        <v>0.14130315315177219</v>
+        <v>0.14131899672000273</v>
       </c>
       <c r="G8" s="3">
-        <v>0.14010543126721611</v>
+        <v>0.14007751075560923</v>
       </c>
       <c r="H8" s="2">
-        <v>0.00119772188455608</v>
+        <v>0.0012414859643934961</v>
       </c>
       <c r="I8" s="4">
-        <v>27.512355307242899</v>
+        <v>27.512893076988803</v>
       </c>
       <c r="J8" s="4">
-        <v>27.509822168331084</v>
+        <v>27.509825676020284</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0025331389118150582</v>
+        <v>0.003067400968518541</v>
       </c>
       <c r="L8" s="4">
-        <v>1.0272079341483216</v>
+        <v>1.027268297176029</v>
       </c>
       <c r="M8" s="4">
-        <v>1.027493474753322</v>
+        <v>1.0272102372843954</v>
       </c>
       <c r="N8" s="2">
-        <v>0.00028554060500041167</v>
+        <v>5.805989163354397e-05</v>
       </c>
       <c r="O8" s="8" t="b">
         <v>1</v>
@@ -2460,31 +2460,31 @@
         <v>0.73719999999999997</v>
       </c>
       <c r="F9" s="3">
-        <v>0.13887674172559755</v>
+        <v>0.13887686923564996</v>
       </c>
       <c r="G9" s="3">
-        <v>0.14189877917576141</v>
+        <v>0.14189419634294137</v>
       </c>
       <c r="H9" s="2">
-        <v>0.0030220374501638558</v>
+        <v>0.0030173271072914121</v>
       </c>
       <c r="I9" s="4">
-        <v>27.501981530869159</v>
+        <v>27.502192885681211</v>
       </c>
       <c r="J9" s="4">
-        <v>27.517682161965524</v>
+        <v>27.516436676219485</v>
       </c>
       <c r="K9" s="2">
-        <v>0.015700631096365214</v>
+        <v>0.014243790538273515</v>
       </c>
       <c r="L9" s="4">
-        <v>1.0243518368777123</v>
+        <v>1.024469370652427</v>
       </c>
       <c r="M9" s="4">
-        <v>1.0288068860189061</v>
+        <v>1.0287602813150911</v>
       </c>
       <c r="N9" s="2">
-        <v>0.0044550491411938786</v>
+        <v>0.0042909106626640714</v>
       </c>
       <c r="O9" s="8" t="b">
         <v>1</v>
@@ -2538,31 +2538,31 @@
         <v>0.5</v>
       </c>
       <c r="F10" s="3">
-        <v>0.15227385452346909</v>
+        <v>0.15227779833515845</v>
       </c>
       <c r="G10" s="3">
-        <v>0.13246967422071301</v>
+        <v>0.13246848087127022</v>
       </c>
       <c r="H10" s="2">
-        <v>0.019804180302756075</v>
+        <v>0.019809317463888226</v>
       </c>
       <c r="I10" s="4">
-        <v>27.552840081872716</v>
+        <v>27.550671916098338</v>
       </c>
       <c r="J10" s="4">
-        <v>27.472183313917242</v>
+        <v>27.472156375068892</v>
       </c>
       <c r="K10" s="2">
-        <v>0.080656767955474607</v>
+        <v>0.078515541029446467</v>
       </c>
       <c r="L10" s="4">
-        <v>1.0342972954602669</v>
+        <v>1.0343009152169567</v>
       </c>
       <c r="M10" s="4">
-        <v>1.022673707655869</v>
+        <v>1.0223352849934766</v>
       </c>
       <c r="N10" s="2">
-        <v>0.011623587804397983</v>
+        <v>0.011965630223480073</v>
       </c>
       <c r="O10" s="8" t="b">
         <v>1</v>
@@ -2616,31 +2616,31 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="F11" s="3">
-        <v>0.1407260861420018</v>
+        <v>0.14072673911407582</v>
       </c>
       <c r="G11" s="3">
-        <v>0.14071211271902143</v>
+        <v>0.1407227431818735</v>
       </c>
       <c r="H11" s="2">
-        <v>1.3973422980373407e-05</v>
+        <v>3.9959322023219723e-06</v>
       </c>
       <c r="I11" s="4">
-        <v>27.511445889463403</v>
+        <v>27.511444539383717</v>
       </c>
       <c r="J11" s="4">
-        <v>27.511352407873005</v>
+        <v>27.510840607904697</v>
       </c>
       <c r="K11" s="2">
-        <v>9.3481590397459513e-05</v>
+        <v>0.00060393147902004785</v>
       </c>
       <c r="L11" s="4">
-        <v>1.0274875714872385</v>
+        <v>1.0274904739264787</v>
       </c>
       <c r="M11" s="4">
-        <v>1.0271907147046338</v>
+        <v>1.0274751432406724</v>
       </c>
       <c r="N11" s="2">
-        <v>0.00029685678260471526</v>
+        <v>1.5330685806391742e-05</v>
       </c>
       <c r="O11" s="8" t="b">
         <v>1</v>
@@ -2694,31 +2694,31 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="F12" s="3">
-        <v>0.14111142809713401</v>
+        <v>0.14111167993902346</v>
       </c>
       <c r="G12" s="3">
-        <v>0.14011441325431476</v>
+        <v>0.1401248630231198</v>
       </c>
       <c r="H12" s="2">
-        <v>0.00099701484281924935</v>
+        <v>0.00098681691590365994</v>
       </c>
       <c r="I12" s="4">
-        <v>27.514702848520869</v>
+        <v>27.51470033598747</v>
       </c>
       <c r="J12" s="4">
-        <v>27.508772092975221</v>
+        <v>27.50831037016934</v>
       </c>
       <c r="K12" s="2">
-        <v>0.0059307555456484806</v>
+        <v>0.0063899658181298946</v>
       </c>
       <c r="L12" s="4">
-        <v>1.0263732122872236</v>
+        <v>1.026377500982381</v>
       </c>
       <c r="M12" s="4">
-        <v>1.029915887267715</v>
+        <v>1.0293921699543067</v>
       </c>
       <c r="N12" s="2">
-        <v>0.0035426749804914337</v>
+        <v>0.0030146689719257047</v>
       </c>
       <c r="O12" s="8" t="b">
         <v>1</v>
@@ -2772,31 +2772,31 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F13" s="3">
-        <v>0.14290902866897046</v>
+        <v>0.14292499959429997</v>
       </c>
       <c r="G13" s="3">
-        <v>0.1383832947830333</v>
+        <v>0.1383819724534982</v>
       </c>
       <c r="H13" s="2">
-        <v>0.004525733885937161</v>
+        <v>0.0045430271408017642</v>
       </c>
       <c r="I13" s="4">
-        <v>27.557902445964487</v>
+        <v>27.556735396817885</v>
       </c>
       <c r="J13" s="4">
-        <v>27.565946610313404</v>
+        <v>27.568103379388219</v>
       </c>
       <c r="K13" s="2">
-        <v>0.0080441643489166381</v>
+        <v>0.011367982570334334</v>
       </c>
       <c r="L13" s="4">
-        <v>1.0553514041607499</v>
+        <v>1.055344220243412</v>
       </c>
       <c r="M13" s="4">
-        <v>1.003629195831385</v>
+        <v>1.0035259433226347</v>
       </c>
       <c r="N13" s="2">
-        <v>0.051722208329364916</v>
+        <v>0.05181827692077734</v>
       </c>
       <c r="O13" s="8" t="b">
         <v>1</v>
@@ -2850,31 +2850,31 @@
         <v>-0.074999999999999997</v>
       </c>
       <c r="F14" s="3">
-        <v>0.14071460078989673</v>
+        <v>0.14072711756760684</v>
       </c>
       <c r="G14" s="3">
-        <v>0.14070479246439427</v>
+        <v>0.14072278367373861</v>
       </c>
       <c r="H14" s="2">
-        <v>9.8083255024583593e-06</v>
+        <v>4.3338938682246919e-06</v>
       </c>
       <c r="I14" s="4">
-        <v>27.510890931943493</v>
+        <v>27.510568017389517</v>
       </c>
       <c r="J14" s="4">
-        <v>27.511337667946691</v>
+        <v>27.511355594716974</v>
       </c>
       <c r="K14" s="2">
-        <v>0.00044673600319811158</v>
+        <v>0.00078757732745771136</v>
       </c>
       <c r="L14" s="4">
-        <v>1.0273672089391885</v>
+        <v>1.0275397898210152</v>
       </c>
       <c r="M14" s="4">
-        <v>1.0272124026309004</v>
+        <v>1.0272375350002043</v>
       </c>
       <c r="N14" s="2">
-        <v>0.00015480630828812458</v>
+        <v>0.00030225482081092103</v>
       </c>
       <c r="O14" s="8" t="b">
         <v>1</v>
@@ -2928,31 +2928,31 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="F15" s="3">
-        <v>0.13815035366773262</v>
+        <v>0.13814203415021617</v>
       </c>
       <c r="G15" s="3">
-        <v>0.14335343253664351</v>
+        <v>0.14334108294218698</v>
       </c>
       <c r="H15" s="2">
-        <v>0.0052030788689108876</v>
+        <v>0.0051990487919708062</v>
       </c>
       <c r="I15" s="4">
-        <v>27.519363083255712</v>
+        <v>27.520511173508282</v>
       </c>
       <c r="J15" s="4">
-        <v>27.498978464224649</v>
+        <v>27.498912369667721</v>
       </c>
       <c r="K15" s="2">
-        <v>0.020384619031062812</v>
+        <v>0.021598803840561232</v>
       </c>
       <c r="L15" s="4">
-        <v>1.0285389198951425</v>
+        <v>1.0286493103414238</v>
       </c>
       <c r="M15" s="4">
-        <v>1.0261521405383529</v>
+        <v>1.0255475113300581</v>
       </c>
       <c r="N15" s="2">
-        <v>0.0023867793567895479</v>
+        <v>0.0031017990113657579</v>
       </c>
       <c r="O15" s="8" t="b">
         <v>1</v>
@@ -3006,31 +3006,31 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F16" s="3">
-        <v>0.14185635647684128</v>
+        <v>0.14185370972241501</v>
       </c>
       <c r="G16" s="3">
-        <v>0.13867654821692285</v>
+        <v>0.13867622055760456</v>
       </c>
       <c r="H16" s="2">
-        <v>0.0031798082599184263</v>
+        <v>0.0031774891648104486</v>
       </c>
       <c r="I16" s="4">
-        <v>27.358991802789149</v>
+        <v>27.359264837573221</v>
       </c>
       <c r="J16" s="4">
-        <v>27.571358918091278</v>
+        <v>27.571391984856575</v>
       </c>
       <c r="K16" s="2">
-        <v>0.21236711530212915</v>
+        <v>0.21212714728335413</v>
       </c>
       <c r="L16" s="4">
-        <v>1.0469414461448439</v>
+        <v>1.0469589233919687</v>
       </c>
       <c r="M16" s="4">
-        <v>1.0038238266425243</v>
+        <v>1.0038233532509258</v>
       </c>
       <c r="N16" s="2">
-        <v>0.043117619502319515</v>
+        <v>0.043135570141042967</v>
       </c>
       <c r="O16" s="8" t="b">
         <v>1</v>
@@ -3084,31 +3084,31 @@
         <v>0.065000000000000002</v>
       </c>
       <c r="F17" s="3">
-        <v>0.13620324385504221</v>
+        <v>0.13620916916354084</v>
       </c>
       <c r="G17" s="3">
-        <v>0.14716395710258351</v>
+        <v>0.14715698693025592</v>
       </c>
       <c r="H17" s="2">
-        <v>0.010960713247541304</v>
+        <v>0.010947817766715079</v>
       </c>
       <c r="I17" s="4">
-        <v>27.539550413446932</v>
+        <v>27.540156398863701</v>
       </c>
       <c r="J17" s="4">
-        <v>27.447999643343451</v>
+        <v>27.447995083304193</v>
       </c>
       <c r="K17" s="2">
-        <v>0.091550770103481227</v>
+        <v>0.092161315559508239</v>
       </c>
       <c r="L17" s="4">
-        <v>1.0174344851376125</v>
+        <v>1.017580245702765</v>
       </c>
       <c r="M17" s="4">
-        <v>1.0488403847338745</v>
+        <v>1.0487477512872843</v>
       </c>
       <c r="N17" s="2">
-        <v>0.031405899596262055</v>
+        <v>0.031167505584519306</v>
       </c>
       <c r="O17" s="8" t="b">
         <v>1</v>
@@ -3162,31 +3162,31 @@
         <v>0.81599999999999995</v>
       </c>
       <c r="F18" s="3">
-        <v>0.13520110310583283</v>
+        <v>0.13521529657307829</v>
       </c>
       <c r="G18" s="3">
-        <v>0.14411928790539444</v>
+        <v>0.14412903907857397</v>
       </c>
       <c r="H18" s="2">
-        <v>0.008918184799561607</v>
+        <v>0.0089137425054956754</v>
       </c>
       <c r="I18" s="4">
-        <v>27.521047393470155</v>
+        <v>27.521220626552747</v>
       </c>
       <c r="J18" s="4">
-        <v>27.512910439540917</v>
+        <v>27.51291137554972</v>
       </c>
       <c r="K18" s="2">
-        <v>0.0081369539292381887</v>
+        <v>0.0083092510030269295</v>
       </c>
       <c r="L18" s="4">
-        <v>1.0494521159515722</v>
+        <v>1.0492548199912586</v>
       </c>
       <c r="M18" s="4">
-        <v>1.0128430601073966</v>
+        <v>1.0127417441616515</v>
       </c>
       <c r="N18" s="2">
-        <v>0.03660905584417562</v>
+        <v>0.036513075829607056</v>
       </c>
       <c r="O18" s="8" t="b">
         <v>1</v>
@@ -3240,31 +3240,31 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F19" s="3">
-        <v>0.13572201763918509</v>
+        <v>0.13572277706593006</v>
       </c>
       <c r="G19" s="3">
-        <v>0.1497266396343167</v>
+        <v>0.14975483224638045</v>
       </c>
       <c r="H19" s="2">
-        <v>0.014004621995131611</v>
+        <v>0.014032055180450392</v>
       </c>
       <c r="I19" s="4">
-        <v>27.56119071107139</v>
+        <v>27.561190222552511</v>
       </c>
       <c r="J19" s="4">
-        <v>27.378589954010124</v>
+        <v>27.378585866107585</v>
       </c>
       <c r="K19" s="2">
-        <v>0.18260075706126599</v>
+        <v>0.18260435644492645</v>
       </c>
       <c r="L19" s="4">
-        <v>1.0053650288962739</v>
+        <v>1.0053833213441219</v>
       </c>
       <c r="M19" s="4">
-        <v>1.090991339662871</v>
+        <v>1.0912191033996717</v>
       </c>
       <c r="N19" s="2">
-        <v>0.085626310766597102</v>
+        <v>0.085835782055549759</v>
       </c>
       <c r="O19" s="8" t="b">
         <v>1</v>
@@ -3318,31 +3318,31 @@
         <v>0.18708</v>
       </c>
       <c r="F20" s="3">
-        <v>0.14074351600194032</v>
+        <v>0.14074794126269605</v>
       </c>
       <c r="G20" s="3">
-        <v>0.14070651148638524</v>
+        <v>0.14070749083020645</v>
       </c>
       <c r="H20" s="2">
-        <v>3.7004515555077999e-05</v>
+        <v>4.0450432489597121e-05</v>
       </c>
       <c r="I20" s="4">
-        <v>27.502971441751242</v>
+        <v>27.502152596929022</v>
       </c>
       <c r="J20" s="4">
-        <v>27.519582506748691</v>
+        <v>27.519582006024905</v>
       </c>
       <c r="K20" s="2">
-        <v>0.016611064997448466</v>
+        <v>0.01742940909588242</v>
       </c>
       <c r="L20" s="4">
-        <v>1.028193553445879</v>
+        <v>1.028962928144316</v>
       </c>
       <c r="M20" s="4">
-        <v>1.0256320135904902</v>
+        <v>1.0256343923338207</v>
       </c>
       <c r="N20" s="2">
-        <v>0.0025615398553888724</v>
+        <v>0.0033285358104953033</v>
       </c>
       <c r="O20" s="8" t="b">
         <v>1</v>
@@ -3396,31 +3396,31 @@
         <v>0.48899999999999999</v>
       </c>
       <c r="F21" s="3">
-        <v>0.14038846250062179</v>
+        <v>0.14039073919256095</v>
       </c>
       <c r="G21" s="3">
-        <v>0.14119587544954856</v>
+        <v>0.14120479915537507</v>
       </c>
       <c r="H21" s="2">
-        <v>0.00080741294892677784</v>
+        <v>0.00081405996281411208</v>
       </c>
       <c r="I21" s="4">
-        <v>27.50613860150014</v>
+        <v>27.506139671076483</v>
       </c>
       <c r="J21" s="4">
-        <v>27.518884138073247</v>
+        <v>27.518879327586603</v>
       </c>
       <c r="K21" s="2">
-        <v>0.012745536573106619</v>
+        <v>0.012739656510120767</v>
       </c>
       <c r="L21" s="4">
-        <v>1.029173373650045</v>
+        <v>1.0291723615681629</v>
       </c>
       <c r="M21" s="4">
-        <v>1.0242197289195596</v>
+        <v>1.0238010158686792</v>
       </c>
       <c r="N21" s="2">
-        <v>0.0049536447304854292</v>
+        <v>0.0053713456994837205</v>
       </c>
       <c r="O21" s="8" t="b">
         <v>1</v>
@@ -3474,31 +3474,31 @@
         <v>0.23499999999999999</v>
       </c>
       <c r="F22" s="3">
-        <v>0.15191330538018893</v>
+        <v>0.15188651976761586</v>
       </c>
       <c r="G22" s="3">
-        <v>0.13243042693598986</v>
+        <v>0.13241654011191151</v>
       </c>
       <c r="H22" s="2">
-        <v>0.019482878444199075</v>
+        <v>0.01946997965570435</v>
       </c>
       <c r="I22" s="4">
-        <v>27.526636284054746</v>
+        <v>27.526491821336606</v>
       </c>
       <c r="J22" s="4">
-        <v>27.283736107671018</v>
+        <v>27.283549764333827</v>
       </c>
       <c r="K22" s="2">
-        <v>0.24290017638372774</v>
+        <v>0.24294205700277871</v>
       </c>
       <c r="L22" s="4">
-        <v>1.0041451647108381</v>
+        <v>1.0042952715250046</v>
       </c>
       <c r="M22" s="4">
-        <v>1.0648175617019573</v>
+        <v>1.0648122488457863</v>
       </c>
       <c r="N22" s="2">
-        <v>0.060672396991119149</v>
+        <v>0.060516977320781651</v>
       </c>
       <c r="O22" s="8" t="b">
         <v>1</v>
@@ -3552,31 +3552,31 @@
         <v>0.19208</v>
       </c>
       <c r="F23" s="3">
-        <v>0.14129871808515759</v>
+        <v>0.14133852145066922</v>
       </c>
       <c r="G23" s="3">
-        <v>0.13856393183739699</v>
+        <v>0.13859336566077396</v>
       </c>
       <c r="H23" s="2">
-        <v>0.0027347862477606066</v>
+        <v>0.0027451557898952594</v>
       </c>
       <c r="I23" s="4">
-        <v>27.435636466339418</v>
+        <v>27.436130617040817</v>
       </c>
       <c r="J23" s="4">
-        <v>27.539203242514247</v>
+        <v>27.538495364956191</v>
       </c>
       <c r="K23" s="2">
-        <v>0.10356677617483001</v>
+        <v>0.10236474791537376</v>
       </c>
       <c r="L23" s="4">
-        <v>1.038037872424266</v>
+        <v>1.0382789658339544</v>
       </c>
       <c r="M23" s="4">
-        <v>1.022341694962666</v>
+        <v>1.0223411032797296</v>
       </c>
       <c r="N23" s="2">
-        <v>0.015696177461600014</v>
+        <v>0.015937862554224802</v>
       </c>
       <c r="O23" s="8" t="b">
         <v>1</v>
@@ -3630,31 +3630,31 @@
         <v>0.83899999999999997</v>
       </c>
       <c r="F24" s="3">
-        <v>0.14082369011060417</v>
+        <v>0.1408128223686439</v>
       </c>
       <c r="G24" s="3">
-        <v>0.14067109525517355</v>
+        <v>0.14065793449800804</v>
       </c>
       <c r="H24" s="2">
-        <v>0.00015259485543062112</v>
+        <v>0.0001548878706358614</v>
       </c>
       <c r="I24" s="4">
-        <v>27.514515561885503</v>
+        <v>27.514456143917471</v>
       </c>
       <c r="J24" s="4">
-        <v>27.509337640408148</v>
+        <v>27.508712719160826</v>
       </c>
       <c r="K24" s="2">
-        <v>0.00517792147735463</v>
+        <v>0.0057434247566447994</v>
       </c>
       <c r="L24" s="4">
-        <v>1.0266337757981372</v>
+        <v>1.0263846398413008</v>
       </c>
       <c r="M24" s="4">
-        <v>1.0280621106920635</v>
+        <v>1.0280027595739278</v>
       </c>
       <c r="N24" s="2">
-        <v>0.0014283348939263529</v>
+        <v>0.0016181197326270436</v>
       </c>
       <c r="O24" s="8" t="b">
         <v>1</v>
@@ -3708,31 +3708,31 @@
         <v>0.23499999999999999</v>
       </c>
       <c r="F25" s="3">
-        <v>0.13430979896297091</v>
+        <v>0.13430394326269349</v>
       </c>
       <c r="G25" s="3">
-        <v>0.15558076806935367</v>
+        <v>0.15557906203112093</v>
       </c>
       <c r="H25" s="2">
-        <v>0.021270969106382764</v>
+        <v>0.021275118768427442</v>
       </c>
       <c r="I25" s="4">
-        <v>27.295868426636957</v>
+        <v>27.295654220803556</v>
       </c>
       <c r="J25" s="4">
-        <v>27.468464236312059</v>
+        <v>27.468709361798801</v>
       </c>
       <c r="K25" s="2">
-        <v>0.17259580967510146</v>
+        <v>0.17305514099524544</v>
       </c>
       <c r="L25" s="4">
-        <v>1.0594509825728402</v>
+        <v>1.0593022149742104</v>
       </c>
       <c r="M25" s="4">
-        <v>1.0017833739729074</v>
+        <v>1.0017152316479685</v>
       </c>
       <c r="N25" s="2">
-        <v>0.057667608599932807</v>
+        <v>0.057586983326241903</v>
       </c>
       <c r="O25" s="8" t="b">
         <v>1</v>
@@ -3786,31 +3786,31 @@
         <v>0.099782999999999997</v>
       </c>
       <c r="F26" s="3">
-        <v>0.14106021923929518</v>
+        <v>0.1410317476796282</v>
       </c>
       <c r="G26" s="3">
-        <v>0.14102397219691562</v>
+        <v>0.14105098567853944</v>
       </c>
       <c r="H26" s="2">
-        <v>3.6247042379561334e-05</v>
+        <v>1.9237998911236787e-05</v>
       </c>
       <c r="I26" s="4">
-        <v>27.509233659714994</v>
+        <v>27.509937873632282</v>
       </c>
       <c r="J26" s="4">
-        <v>27.50876408749923</v>
+        <v>27.508710200697976</v>
       </c>
       <c r="K26" s="2">
-        <v>0.00046957221576349184</v>
+        <v>0.0012276729343057013</v>
       </c>
       <c r="L26" s="4">
-        <v>1.0261383019311683</v>
+        <v>1.0257314696926547</v>
       </c>
       <c r="M26" s="4">
-        <v>1.0262526725630037</v>
+        <v>1.025611654486984</v>
       </c>
       <c r="N26" s="2">
-        <v>0.00011437063183539209</v>
+        <v>0.00011981520567072579</v>
       </c>
       <c r="O26" s="8" t="b">
         <v>1</v>
@@ -3864,31 +3864,31 @@
         <v>0.54198999999999997</v>
       </c>
       <c r="F27" s="3">
-        <v>0.14186426970955471</v>
+        <v>0.14186259344825103</v>
       </c>
       <c r="G27" s="3">
-        <v>0.13924135504680843</v>
+        <v>0.13923625085419725</v>
       </c>
       <c r="H27" s="2">
-        <v>0.0026229146627462785</v>
+        <v>0.0026263425940537821</v>
       </c>
       <c r="I27" s="4">
-        <v>27.499906806045203</v>
+        <v>27.49990333215618</v>
       </c>
       <c r="J27" s="4">
-        <v>27.523749842465179</v>
+        <v>27.522871180623326</v>
       </c>
       <c r="K27" s="2">
-        <v>0.023843036419975761</v>
+        <v>0.022967848467146723</v>
       </c>
       <c r="L27" s="4">
-        <v>1.0204020711363022</v>
+        <v>1.0209444987911978</v>
       </c>
       <c r="M27" s="4">
-        <v>1.0341878021948303</v>
+        <v>1.034189620075459</v>
       </c>
       <c r="N27" s="2">
-        <v>0.013785731058528095</v>
+        <v>0.013245121284261252</v>
       </c>
       <c r="O27" s="8" t="b">
         <v>1</v>
@@ -3942,31 +3942,31 @@
         <v>0.57586000000000004</v>
       </c>
       <c r="F28" s="3">
-        <v>0.14205061962983309</v>
+        <v>0.14204856441108973</v>
       </c>
       <c r="G28" s="3">
-        <v>0.1398185835719889</v>
+        <v>0.13981837106246523</v>
       </c>
       <c r="H28" s="2">
-        <v>0.0022320360578441945</v>
+        <v>0.0022301933486245096</v>
       </c>
       <c r="I28" s="4">
-        <v>27.503065425810689</v>
+        <v>27.503068376312172</v>
       </c>
       <c r="J28" s="4">
-        <v>27.518258693529333</v>
+        <v>27.517667733309565</v>
       </c>
       <c r="K28" s="2">
-        <v>0.01519326771864371</v>
+        <v>0.014599356997393897</v>
       </c>
       <c r="L28" s="4">
-        <v>1.0210397797565007</v>
+        <v>1.0190357996086785</v>
       </c>
       <c r="M28" s="4">
-        <v>1.032173034609005</v>
+        <v>1.032178017186042</v>
       </c>
       <c r="N28" s="2">
-        <v>0.011133254852504271</v>
+        <v>0.013142217577363446</v>
       </c>
       <c r="O28" s="8" t="b">
         <v>1</v>
@@ -4020,31 +4020,31 @@
         <v>0.079783000000000007</v>
       </c>
       <c r="F29" s="3">
-        <v>0.14083695305788843</v>
+        <v>0.14084411547442904</v>
       </c>
       <c r="G29" s="3">
-        <v>0.14081283700507918</v>
+        <v>0.1408428476958957</v>
       </c>
       <c r="H29" s="2">
-        <v>2.4116052809247668e-05</v>
+        <v>1.2677785333481406e-06</v>
       </c>
       <c r="I29" s="4">
-        <v>27.510064522874131</v>
+        <v>27.510771325289454</v>
       </c>
       <c r="J29" s="4">
-        <v>27.510002170070095</v>
+        <v>27.510766172163699</v>
       </c>
       <c r="K29" s="2">
-        <v>6.2352804036436282e-05</v>
+        <v>5.1531257554415788e-06</v>
       </c>
       <c r="L29" s="4">
-        <v>1.0263449976655188</v>
+        <v>1.02669806328278</v>
       </c>
       <c r="M29" s="4">
-        <v>1.0260671824688661</v>
+        <v>1.0266815919257695</v>
       </c>
       <c r="N29" s="2">
-        <v>0.00027781519665270871</v>
+        <v>1.6471357010550136e-05</v>
       </c>
       <c r="O29" s="8" t="b">
         <v>1</v>
@@ -4098,31 +4098,31 @@
         <v>0.746</v>
       </c>
       <c r="F30" s="3">
-        <v>0.14197368782909883</v>
+        <v>0.14194882449289492</v>
       </c>
       <c r="G30" s="3">
-        <v>0.1395969770038851</v>
+        <v>0.13959506318758969</v>
       </c>
       <c r="H30" s="2">
-        <v>0.0023767108252137348</v>
+        <v>0.0023537613053052353</v>
       </c>
       <c r="I30" s="4">
-        <v>27.503039461205788</v>
+        <v>27.503045184646112</v>
       </c>
       <c r="J30" s="4">
-        <v>27.518513736238845</v>
+        <v>27.518506535089728</v>
       </c>
       <c r="K30" s="2">
-        <v>0.015474275033056983</v>
+        <v>0.015461350443615629</v>
       </c>
       <c r="L30" s="4">
-        <v>1.0212353179746536</v>
+        <v>1.0209882834359434</v>
       </c>
       <c r="M30" s="4">
-        <v>1.0326511015567002</v>
+        <v>1.0326524773604302</v>
       </c>
       <c r="N30" s="2">
-        <v>0.011415783582046535</v>
+        <v>0.01166419392448681</v>
       </c>
       <c r="O30" s="8" t="b">
         <v>1</v>
@@ -4176,31 +4176,31 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="F31" s="3">
-        <v>0.14109291992894729</v>
+        <v>0.14114212898896297</v>
       </c>
       <c r="G31" s="3">
-        <v>0.14019139790899904</v>
+        <v>0.14020406866908966</v>
       </c>
       <c r="H31" s="2">
-        <v>0.00090152201994825321</v>
+        <v>0.00093806031987331284</v>
       </c>
       <c r="I31" s="4">
-        <v>27.506806305446617</v>
+        <v>27.507920454380269</v>
       </c>
       <c r="J31" s="4">
-        <v>27.516191570652836</v>
+        <v>27.515692527169733</v>
       </c>
       <c r="K31" s="2">
-        <v>0.0093852652062196285</v>
+        <v>0.007772072789464346</v>
       </c>
       <c r="L31" s="4">
-        <v>1.0251883062028118</v>
+        <v>1.0252513626704751</v>
       </c>
       <c r="M31" s="4">
-        <v>1.0301873805320614</v>
+        <v>1.0300903877837075</v>
       </c>
       <c r="N31" s="2">
-        <v>0.0049990743292496198</v>
+        <v>0.0048390251132324202</v>
       </c>
       <c r="O31" s="8" t="b">
         <v>1</v>
@@ -4254,31 +4254,31 @@
         <v>0.02</v>
       </c>
       <c r="F32" s="3">
-        <v>0.14072373998505453</v>
+        <v>0.14070501313499273</v>
       </c>
       <c r="G32" s="3">
-        <v>0.14074550195363977</v>
+        <v>0.14073704543034857</v>
       </c>
       <c r="H32" s="2">
-        <v>2.1761968585248814e-05</v>
+        <v>3.2032295355838292e-05</v>
       </c>
       <c r="I32" s="4">
-        <v>27.511450892971197</v>
+        <v>27.511453796804688</v>
       </c>
       <c r="J32" s="4">
-        <v>27.511331173330632</v>
+        <v>27.511335981675984</v>
       </c>
       <c r="K32" s="2">
-        <v>0.00011971964056556317</v>
+        <v>0.00011781512870356892</v>
       </c>
       <c r="L32" s="4">
-        <v>1.0273618259868598</v>
+        <v>1.0267888326859147</v>
       </c>
       <c r="M32" s="4">
-        <v>1.0274135113818219</v>
+        <v>1.0274799552762877</v>
       </c>
       <c r="N32" s="2">
-        <v>5.1685394962142084e-05</v>
+        <v>0.0006911225903729612</v>
       </c>
       <c r="O32" s="8" t="b">
         <v>1</v>
@@ -4332,31 +4332,31 @@
         <v>0.75</v>
       </c>
       <c r="F33" s="3">
-        <v>0.14073854632156666</v>
+        <v>0.14072929516855323</v>
       </c>
       <c r="G33" s="3">
-        <v>0.14073125123924179</v>
+        <v>0.14071737223593409</v>
       </c>
       <c r="H33" s="2">
-        <v>7.2950823248596475e-06</v>
+        <v>1.192293261914612e-05</v>
       </c>
       <c r="I33" s="4">
-        <v>27.510925224505058</v>
+        <v>27.511360726355747</v>
       </c>
       <c r="J33" s="4">
-        <v>27.51141496364744</v>
+        <v>27.511414743355545</v>
       </c>
       <c r="K33" s="2">
-        <v>0.00048973914238104044</v>
+        <v>5.4016999797568133e-05</v>
       </c>
       <c r="L33" s="4">
-        <v>1.027365153566459</v>
+        <v>1.0270352829397356</v>
       </c>
       <c r="M33" s="4">
-        <v>1.0274741361076212</v>
+        <v>1.0269348750238925</v>
       </c>
       <c r="N33" s="2">
-        <v>0.00010898254116220585</v>
+        <v>0.00010040791584309261</v>
       </c>
       <c r="O33" s="8" t="b">
         <v>1</v>
@@ -4410,31 +4410,31 @@
         <v>0.34999999999999998</v>
       </c>
       <c r="F34" s="3">
-        <v>0.14069516436287205</v>
+        <v>0.14071236793971451</v>
       </c>
       <c r="G34" s="3">
-        <v>0.14072747421819307</v>
+        <v>0.14074787910625036</v>
       </c>
       <c r="H34" s="2">
-        <v>3.2309855321016601e-05</v>
+        <v>3.5511166535856509e-05</v>
       </c>
       <c r="I34" s="4">
-        <v>27.510704089935757</v>
+        <v>27.511464992899391</v>
       </c>
       <c r="J34" s="4">
-        <v>27.510451701491036</v>
+        <v>27.511333435171537</v>
       </c>
       <c r="K34" s="2">
-        <v>0.00025238844472141864</v>
+        <v>0.00013155772785466979</v>
       </c>
       <c r="L34" s="4">
-        <v>1.0271644384612075</v>
+        <v>1.02710335036503</v>
       </c>
       <c r="M34" s="4">
-        <v>1.0274029832667897</v>
+        <v>1.0274573384126577</v>
       </c>
       <c r="N34" s="2">
-        <v>0.00023854480558216373</v>
+        <v>0.00035398804762776237</v>
       </c>
       <c r="O34" s="8" t="b">
         <v>1</v>
@@ -4488,31 +4488,31 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="F35" s="3">
-        <v>0.14230768095986385</v>
+        <v>0.14231552420152388</v>
       </c>
       <c r="G35" s="3">
-        <v>0.13931470337038288</v>
+        <v>0.13930394667531965</v>
       </c>
       <c r="H35" s="2">
-        <v>0.0029929775894809718</v>
+        <v>0.0030115775262042344</v>
       </c>
       <c r="I35" s="4">
-        <v>27.49433444139089</v>
+        <v>27.494340475328556</v>
       </c>
       <c r="J35" s="4">
-        <v>27.528162439574317</v>
+        <v>27.527605639728733</v>
       </c>
       <c r="K35" s="2">
-        <v>0.033827998183426189</v>
+        <v>0.033265164400177127</v>
       </c>
       <c r="L35" s="4">
-        <v>1.0174436128081832</v>
+        <v>1.01611073076764</v>
       </c>
       <c r="M35" s="4">
-        <v>1.036954964265776</v>
+        <v>1.0371579378002398</v>
       </c>
       <c r="N35" s="2">
-        <v>0.019511351457592863</v>
+        <v>0.021047207032599769</v>
       </c>
       <c r="O35" s="8" t="b">
         <v>1</v>
@@ -4566,31 +4566,31 @@
         <v>0.83750000000000002</v>
       </c>
       <c r="F36" s="3">
-        <v>0.14498662526248368</v>
+        <v>0.14502695149589942</v>
       </c>
       <c r="G36" s="3">
-        <v>0.13712880403130276</v>
+        <v>0.13713751698204471</v>
       </c>
       <c r="H36" s="2">
-        <v>0.0078578212311809226</v>
+        <v>0.0078894345138547095</v>
       </c>
       <c r="I36" s="4">
-        <v>27.520697521351849</v>
+        <v>27.520382254871265</v>
       </c>
       <c r="J36" s="4">
-        <v>27.50343713777113</v>
+        <v>27.503423576486682</v>
       </c>
       <c r="K36" s="2">
-        <v>0.017260383580719463</v>
+        <v>0.016958678384582981</v>
       </c>
       <c r="L36" s="4">
-        <v>1.024367225097548</v>
+        <v>1.0243074679460642</v>
       </c>
       <c r="M36" s="4">
-        <v>1.0310033271676467</v>
+        <v>1.0310078761568471</v>
       </c>
       <c r="N36" s="2">
-        <v>0.0066361020700986817</v>
+        <v>0.0067004082107828822</v>
       </c>
       <c r="O36" s="8" t="b">
         <v>1</v>
@@ -4644,31 +4644,31 @@
         <v>0.38</v>
       </c>
       <c r="F37" s="3">
-        <v>0.14697629373238935</v>
+        <v>0.14697510665070623</v>
       </c>
       <c r="G37" s="3">
-        <v>0.1345950324455038</v>
+        <v>0.13458474767989148</v>
       </c>
       <c r="H37" s="2">
-        <v>0.012381261286885548</v>
+        <v>0.012390358970814752</v>
       </c>
       <c r="I37" s="4">
-        <v>27.494476614639666</v>
+        <v>27.494511082985298</v>
       </c>
       <c r="J37" s="4">
-        <v>27.540841226762325</v>
+        <v>27.541639846043324</v>
       </c>
       <c r="K37" s="2">
-        <v>0.046364612122658855</v>
+        <v>0.04712876305802638</v>
       </c>
       <c r="L37" s="4">
-        <v>1.0208179839011968</v>
+        <v>1.0211888420276363</v>
       </c>
       <c r="M37" s="4">
-        <v>1.0316530568262776</v>
+        <v>1.0312350306917837</v>
       </c>
       <c r="N37" s="2">
-        <v>0.010835072925080791</v>
+        <v>0.010046188664147415</v>
       </c>
       <c r="O37" s="8" t="b">
         <v>1</v>
@@ -4722,31 +4722,31 @@
         <v>-0.25</v>
       </c>
       <c r="F38" s="3">
-        <v>0.14782498678257339</v>
+        <v>0.14784187933682175</v>
       </c>
       <c r="G38" s="3">
-        <v>0.12962737222551801</v>
+        <v>0.12960598166238102</v>
       </c>
       <c r="H38" s="2">
-        <v>0.018197614557055375</v>
+        <v>0.018235897674440726</v>
       </c>
       <c r="I38" s="4">
-        <v>27.510986913418208</v>
+        <v>27.511401041972192</v>
       </c>
       <c r="J38" s="4">
-        <v>27.51137661338845</v>
+        <v>27.510741849635679</v>
       </c>
       <c r="K38" s="2">
-        <v>0.00038969997024196346</v>
+        <v>0.0006591923365135699</v>
       </c>
       <c r="L38" s="4">
-        <v>1.0161354760887367</v>
+        <v>1.0163440822147765</v>
       </c>
       <c r="M38" s="4">
-        <v>1.0471073199709886</v>
+        <v>1.0471629833900007</v>
       </c>
       <c r="N38" s="2">
-        <v>0.030971843882251937</v>
+        <v>0.030818901175224234</v>
       </c>
       <c r="O38" s="8" t="b">
         <v>1</v>
@@ -4800,31 +4800,31 @@
         <v>0.63</v>
       </c>
       <c r="F39" s="3">
-        <v>0.14072649429716594</v>
+        <v>0.14072643020168821</v>
       </c>
       <c r="G39" s="3">
-        <v>0.14073507233730542</v>
+        <v>0.14071419185488135</v>
       </c>
       <c r="H39" s="2">
-        <v>8.5780401394841554e-06</v>
+        <v>1.2238346806858758e-05</v>
       </c>
       <c r="I39" s="4">
-        <v>27.511397870762323</v>
+        <v>27.510685747665434</v>
       </c>
       <c r="J39" s="4">
-        <v>27.510746696106935</v>
+        <v>27.510704872663268</v>
       </c>
       <c r="K39" s="2">
-        <v>0.0006511746553883313</v>
+        <v>1.9124997834296664e-05</v>
       </c>
       <c r="L39" s="4">
-        <v>1.0274626664296907</v>
+        <v>1.0269707395992576</v>
       </c>
       <c r="M39" s="4">
-        <v>1.0271720387659724</v>
+        <v>1.0273951492640623</v>
       </c>
       <c r="N39" s="2">
-        <v>0.00029062766371823479</v>
+        <v>0.00042440966480472575</v>
       </c>
       <c r="O39" s="8" t="b">
         <v>1</v>
@@ -4878,31 +4878,31 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F40" s="3">
-        <v>0.14014973745899126</v>
+        <v>0.1401488885932228</v>
       </c>
       <c r="G40" s="3">
-        <v>0.14129264245396833</v>
+        <v>0.14129541646162647</v>
       </c>
       <c r="H40" s="2">
-        <v>0.0011429049949770731</v>
+        <v>0.0011465278684036628</v>
       </c>
       <c r="I40" s="4">
-        <v>27.511415200482247</v>
+        <v>27.510666574847903</v>
       </c>
       <c r="J40" s="4">
-        <v>27.511519994678054</v>
+        <v>27.510835730128974</v>
       </c>
       <c r="K40" s="2">
-        <v>0.00010479419580633476</v>
+        <v>0.00016915528107119826</v>
       </c>
       <c r="L40" s="4">
-        <v>1.0277876850496561</v>
+        <v>1.0281839890237976</v>
       </c>
       <c r="M40" s="4">
-        <v>1.0261074891067381</v>
+        <v>1.0260871753571539</v>
       </c>
       <c r="N40" s="2">
-        <v>0.0016801959429180169</v>
+        <v>0.0020968136666437154</v>
       </c>
       <c r="O40" s="8" t="b">
         <v>1</v>
@@ -4956,31 +4956,31 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>0.12961332423902663</v>
+        <v>0.12961263990383026</v>
       </c>
       <c r="G41" s="3">
-        <v>0.14782757704496471</v>
+        <v>0.14783982040942517</v>
       </c>
       <c r="H41" s="2">
-        <v>0.01821425280593808</v>
+        <v>0.018227180505594909</v>
       </c>
       <c r="I41" s="4">
-        <v>27.510995397845932</v>
+        <v>27.511392589872799</v>
       </c>
       <c r="J41" s="4">
-        <v>27.51057801257673</v>
+        <v>27.510589816348784</v>
       </c>
       <c r="K41" s="2">
-        <v>0.00041738526920198638</v>
+        <v>0.00080277352401481039</v>
       </c>
       <c r="L41" s="4">
-        <v>1.0470527511506009</v>
+        <v>1.0470918921837924</v>
       </c>
       <c r="M41" s="4">
-        <v>1.0158883106408876</v>
+        <v>1.0162654266951499</v>
       </c>
       <c r="N41" s="2">
-        <v>0.031164440509713343</v>
+        <v>0.030826465488642541</v>
       </c>
       <c r="O41" s="8" t="b">
         <v>1</v>
@@ -5034,31 +5034,31 @@
         <v>0.65000000000000002</v>
       </c>
       <c r="F42" s="3">
-        <v>0.14773159030990588</v>
+        <v>0.14771026481032837</v>
       </c>
       <c r="G42" s="3">
-        <v>0.13358439845450429</v>
+        <v>0.13357688576746793</v>
       </c>
       <c r="H42" s="2">
-        <v>0.014147191855401586</v>
+        <v>0.014133379042860439</v>
       </c>
       <c r="I42" s="4">
-        <v>27.511394687667632</v>
+        <v>27.510580922913277</v>
       </c>
       <c r="J42" s="4">
-        <v>27.511394746813323</v>
+        <v>27.511400787047762</v>
       </c>
       <c r="K42" s="2">
-        <v>5.9145691011508461e-08</v>
+        <v>0.00081986413448476014</v>
       </c>
       <c r="L42" s="4">
-        <v>1.0152044350624183</v>
+        <v>1.0151648271006628</v>
       </c>
       <c r="M42" s="4">
-        <v>1.0394922579743049</v>
+        <v>1.0390684164512825</v>
       </c>
       <c r="N42" s="2">
-        <v>0.024287822911886581</v>
+        <v>0.023903589350619647</v>
       </c>
       <c r="O42" s="8" t="b">
         <v>1</v>
@@ -5112,31 +5112,31 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="F43" s="3">
-        <v>0.14164876838070562</v>
+        <v>0.1416075473065144</v>
       </c>
       <c r="G43" s="3">
-        <v>0.13976804439380586</v>
+        <v>0.13977515822344</v>
       </c>
       <c r="H43" s="2">
-        <v>0.0018807239868997572</v>
+        <v>0.0018323890830743983</v>
       </c>
       <c r="I43" s="4">
-        <v>27.510405855081388</v>
+        <v>27.51137447151649</v>
       </c>
       <c r="J43" s="4">
-        <v>27.510739403039679</v>
+        <v>27.510520484644928</v>
       </c>
       <c r="K43" s="2">
-        <v>0.00033354795829154682</v>
+        <v>0.00085398687156157393</v>
       </c>
       <c r="L43" s="4">
-        <v>1.0254223054372371</v>
+        <v>1.0256967023793668</v>
       </c>
       <c r="M43" s="4">
-        <v>1.0291882138939155</v>
+        <v>1.0293572856573874</v>
       </c>
       <c r="N43" s="2">
-        <v>0.0037659084566783463</v>
+        <v>0.0036605832780205461</v>
       </c>
       <c r="O43" s="8" t="b">
         <v>1</v>
@@ -5190,31 +5190,31 @@
         <v>7600</v>
       </c>
       <c r="F44" s="3">
-        <v>0.14125637520199474</v>
+        <v>0.14128834909355756</v>
       </c>
       <c r="G44" s="3">
-        <v>0.13995018306917634</v>
+        <v>0.13992173478982442</v>
       </c>
       <c r="H44" s="2">
-        <v>0.0013061921328184067</v>
+        <v>0.001366614303733138</v>
       </c>
       <c r="I44" s="4">
-        <v>27.511068143085993</v>
+        <v>27.511080144903588</v>
       </c>
       <c r="J44" s="4">
-        <v>27.51113000486248</v>
+        <v>27.512116995978602</v>
       </c>
       <c r="K44" s="2">
-        <v>6.1861776487148745e-05</v>
+        <v>0.0010368510750140558</v>
       </c>
       <c r="L44" s="4">
-        <v>1.034573983346031</v>
+        <v>1.0346059833475107</v>
       </c>
       <c r="M44" s="4">
-        <v>1.0562565834222888</v>
+        <v>1.0562043479096521</v>
       </c>
       <c r="N44" s="2">
-        <v>0.021682600076257774</v>
+        <v>0.02159836456214137</v>
       </c>
       <c r="O44" s="8" t="b">
         <v>1</v>
@@ -5268,28 +5268,28 @@
         <v>-0.085000000000000006</v>
       </c>
       <c r="F45" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="G45" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
       <c r="I45" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="J45" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="K45" s="2">
         <v>0</v>
       </c>
       <c r="L45" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="M45" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="N45" s="2">
         <v>0</v>
@@ -5346,31 +5346,31 @@
         <v>0.065000000000000002</v>
       </c>
       <c r="F46" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="G46" s="3">
-        <v>0.14072627984857264</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="H46" s="2">
-        <v>1.0534981475823768e-05</v>
+        <v>0</v>
       </c>
       <c r="I46" s="4">
-        <v>27.511393450254957</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="J46" s="4">
-        <v>27.511397910621099</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="K46" s="2">
-        <v>4.4603661422115693e-06</v>
+        <v>0</v>
       </c>
       <c r="L46" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="M46" s="4">
-        <v>1.0274158185617246</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="N46" s="2">
-        <v>0.0001649829569911887</v>
+        <v>0</v>
       </c>
       <c r="O46" s="8" t="b">
         <v>1</v>
@@ -5424,31 +5424,31 @@
         <v>58000</v>
       </c>
       <c r="F47" s="3">
-        <v>0.14088288053032103</v>
+        <v>0.14086266892922453</v>
       </c>
       <c r="G47" s="3">
-        <v>0.1397514612663881</v>
+        <v>0.13973977177967867</v>
       </c>
       <c r="H47" s="2">
-        <v>0.0011314192639329257</v>
+        <v>0.0011228971495458595</v>
       </c>
       <c r="I47" s="4">
-        <v>27.495851793611621</v>
+        <v>27.494366959821548</v>
       </c>
       <c r="J47" s="4">
-        <v>27.531399660938348</v>
+        <v>27.531876034018808</v>
       </c>
       <c r="K47" s="2">
-        <v>0.035547867326727101</v>
+        <v>0.037509074197259906</v>
       </c>
       <c r="L47" s="4">
-        <v>1.0251255999398841</v>
+        <v>1.0245015635023307</v>
       </c>
       <c r="M47" s="4">
-        <v>1.0290498635504595</v>
+        <v>1.0291755094985926</v>
       </c>
       <c r="N47" s="2">
-        <v>0.003924263610575407</v>
+        <v>0.004673945996261919</v>
       </c>
       <c r="O47" s="8" t="b">
         <v>1</v>
@@ -5502,31 +5502,31 @@
         <v>38</v>
       </c>
       <c r="F48" s="3">
-        <v>0.14662073550324412</v>
+        <v>0.14662161169041726</v>
       </c>
       <c r="G48" s="3">
-        <v>0.13553966810806278</v>
+        <v>0.13553981745930038</v>
       </c>
       <c r="H48" s="2">
-        <v>0.011081067395181332</v>
+        <v>0.011081794231116882</v>
       </c>
       <c r="I48" s="4">
-        <v>27.510697404127029</v>
+        <v>27.510657087491779</v>
       </c>
       <c r="J48" s="4">
-        <v>27.510632193677338</v>
+        <v>27.510669219280828</v>
       </c>
       <c r="K48" s="2">
-        <v>6.5210449690766836e-05</v>
+        <v>1.2131789048908104e-05</v>
       </c>
       <c r="L48" s="4">
-        <v>1.0180018406770086</v>
+        <v>1.0180019428162894</v>
       </c>
       <c r="M48" s="4">
-        <v>1.036112619525239</v>
+        <v>1.0361327789539321</v>
       </c>
       <c r="N48" s="2">
-        <v>0.018110778848230424</v>
+        <v>0.018130836137642659</v>
       </c>
       <c r="O48" s="8" t="b">
         <v>1</v>
@@ -5580,31 +5580,31 @@
         <v>0.15</v>
       </c>
       <c r="F49" s="3">
-        <v>0.14073712768880683</v>
+        <v>0.14070121560806168</v>
       </c>
       <c r="G49" s="3">
-        <v>0.14072315703969443</v>
+        <v>0.14072287671660383</v>
       </c>
       <c r="H49" s="2">
-        <v>1.3970649112404754e-05</v>
+        <v>2.166110854215364e-05</v>
       </c>
       <c r="I49" s="4">
-        <v>27.511433138486723</v>
+        <v>27.511430437951958</v>
       </c>
       <c r="J49" s="4">
-        <v>27.510938019173978</v>
+        <v>27.511342244847015</v>
       </c>
       <c r="K49" s="2">
-        <v>0.00049511931274537346</v>
+        <v>8.8193104943457001e-05</v>
       </c>
       <c r="L49" s="4">
-        <v>1.0275225719736241</v>
+        <v>1.02721044395453</v>
       </c>
       <c r="M49" s="4">
-        <v>1.0275010774411821</v>
+        <v>1.0272749917277424</v>
       </c>
       <c r="N49" s="2">
-        <v>2.1494532441934666e-05</v>
+        <v>6.4547773212408899e-05</v>
       </c>
       <c r="O49" s="8" t="b">
         <v>1</v>
@@ -5658,31 +5658,31 @@
         <v>0.501</v>
       </c>
       <c r="F50" s="3">
-        <v>0.14076133123834303</v>
+        <v>0.14075334814733337</v>
       </c>
       <c r="G50" s="3">
-        <v>0.14062980713959203</v>
+        <v>0.14063796369628054</v>
       </c>
       <c r="H50" s="2">
-        <v>0.00013152409875100135</v>
+        <v>0.00011538445105283013</v>
       </c>
       <c r="I50" s="4">
-        <v>27.510684393105294</v>
+        <v>27.510686769178164</v>
       </c>
       <c r="J50" s="4">
-        <v>27.509359081284458</v>
+        <v>27.509521816761946</v>
       </c>
       <c r="K50" s="2">
-        <v>0.0013253118208353953</v>
+        <v>0.0011649524162180569</v>
       </c>
       <c r="L50" s="4">
-        <v>1.0329268197469581</v>
+        <v>1.0322750674645775</v>
       </c>
       <c r="M50" s="4">
-        <v>1.0199355949752935</v>
+        <v>1.0197409096892984</v>
       </c>
       <c r="N50" s="2">
-        <v>0.012991224771664589</v>
+        <v>0.012534157775279109</v>
       </c>
       <c r="O50" s="8" t="b">
         <v>1</v>
@@ -5736,31 +5736,31 @@
         <v>0.46999999999999997</v>
       </c>
       <c r="F51" s="3">
-        <v>0.13875357315226541</v>
+        <v>0.138742433319792</v>
       </c>
       <c r="G51" s="3">
-        <v>0.1416456941494762</v>
+        <v>0.14164720701776509</v>
       </c>
       <c r="H51" s="2">
-        <v>0.0028921209972107842</v>
+        <v>0.0029047736979730954</v>
       </c>
       <c r="I51" s="4">
-        <v>27.514155543708569</v>
+        <v>27.514353872756033</v>
       </c>
       <c r="J51" s="4">
-        <v>27.506328873617292</v>
+        <v>27.506334283752722</v>
       </c>
       <c r="K51" s="2">
-        <v>0.0078266700912763554</v>
+        <v>0.0080195890033110118</v>
       </c>
       <c r="L51" s="4">
-        <v>1.003592359706831</v>
+        <v>1.0029930481818525</v>
       </c>
       <c r="M51" s="4">
-        <v>1.0536175509104493</v>
+        <v>1.0524839692630887</v>
       </c>
       <c r="N51" s="2">
-        <v>0.050025191203618258</v>
+        <v>0.049490921081236205</v>
       </c>
       <c r="O51" s="8" t="b">
         <v>1</v>
@@ -5814,31 +5814,31 @@
         <v>-0.055</v>
       </c>
       <c r="F52" s="3">
-        <v>0.14073016555950657</v>
+        <v>0.14072619361359762</v>
       </c>
       <c r="G52" s="3">
-        <v>0.14072348602602494</v>
+        <v>0.14073196570564683</v>
       </c>
       <c r="H52" s="2">
-        <v>6.6795334816294183e-06</v>
+        <v>5.7720920492165817e-06</v>
       </c>
       <c r="I52" s="4">
-        <v>27.510718266349272</v>
+        <v>27.511428190616812</v>
       </c>
       <c r="J52" s="4">
-        <v>27.510923105049585</v>
+        <v>27.511333160721563</v>
       </c>
       <c r="K52" s="2">
-        <v>0.00020483870031284823</v>
+        <v>9.5029895248899265e-05</v>
       </c>
       <c r="L52" s="4">
-        <v>1.0273009004349529</v>
+        <v>1.0274189231089079</v>
       </c>
       <c r="M52" s="4">
-        <v>1.027212747435581</v>
+        <v>1.027504934808519</v>
       </c>
       <c r="N52" s="2">
-        <v>8.8152999371926555e-05</v>
+        <v>8.6011699611088233e-05</v>
       </c>
       <c r="O52" s="8" t="b">
         <v>1</v>
@@ -5892,31 +5892,31 @@
         <v>0.501</v>
       </c>
       <c r="F53" s="3">
-        <v>0.14075079946177704</v>
+        <v>0.14074747603698937</v>
       </c>
       <c r="G53" s="3">
-        <v>0.14068271046139058</v>
+        <v>0.14067646943283274</v>
       </c>
       <c r="H53" s="2">
-        <v>6.808900038646204e-05</v>
+        <v>7.1006604156625963e-05</v>
       </c>
       <c r="I53" s="4">
-        <v>27.511035672990545</v>
+        <v>27.511742439930799</v>
       </c>
       <c r="J53" s="4">
-        <v>27.510122323365295</v>
+        <v>27.511083415992459</v>
       </c>
       <c r="K53" s="2">
-        <v>0.00091334962525024821</v>
+        <v>0.00065902393833994211</v>
       </c>
       <c r="L53" s="4">
-        <v>1.0338373218118739</v>
+        <v>1.0339583290268857</v>
       </c>
       <c r="M53" s="4">
-        <v>1.0192863945159485</v>
+        <v>1.019237390972114</v>
       </c>
       <c r="N53" s="2">
-        <v>0.014550927295925442</v>
+        <v>0.014720938054771704</v>
       </c>
       <c r="O53" s="8" t="b">
         <v>1</v>
@@ -5970,31 +5970,31 @@
         <v>0.46999999999999997</v>
       </c>
       <c r="F54" s="3">
-        <v>0.13832748959065552</v>
+        <v>0.13832376310542613</v>
       </c>
       <c r="G54" s="3">
-        <v>0.14229613271601546</v>
+        <v>0.14229234607784547</v>
       </c>
       <c r="H54" s="2">
-        <v>0.0039686431253599386</v>
+        <v>0.0039685829724193378</v>
       </c>
       <c r="I54" s="4">
-        <v>27.506558110389335</v>
+        <v>27.50583532626149</v>
       </c>
       <c r="J54" s="4">
-        <v>27.516182898113243</v>
+        <v>27.516650751262148</v>
       </c>
       <c r="K54" s="2">
-        <v>0.0096247877239079571</v>
+        <v>0.010815425000657797</v>
       </c>
       <c r="L54" s="4">
-        <v>1.0033044765007326</v>
+        <v>1.003314439588294</v>
       </c>
       <c r="M54" s="4">
-        <v>1.0551884216580216</v>
+        <v>1.0549991915702195</v>
       </c>
       <c r="N54" s="2">
-        <v>0.051883945157289002</v>
+        <v>0.051684751981925459</v>
       </c>
       <c r="O54" s="8" t="b">
         <v>1</v>
@@ -6048,31 +6048,31 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="F55" s="3">
-        <v>0.14094692919664328</v>
+        <v>0.14095458139299405</v>
       </c>
       <c r="G55" s="3">
-        <v>0.14051005951874693</v>
+        <v>0.14046242354844449</v>
       </c>
       <c r="H55" s="2">
-        <v>0.00043686967789635656</v>
+        <v>0.00049215784454956224</v>
       </c>
       <c r="I55" s="4">
-        <v>27.510733589987751</v>
+        <v>27.511639168597696</v>
       </c>
       <c r="J55" s="4">
-        <v>27.511288799864928</v>
+        <v>27.511296591308167</v>
       </c>
       <c r="K55" s="2">
-        <v>0.00055520987717727621</v>
+        <v>0.0003425772895297996</v>
       </c>
       <c r="L55" s="4">
-        <v>1.0293365439036859</v>
+        <v>1.0299349098147488</v>
       </c>
       <c r="M55" s="4">
-        <v>1.0242151381620319</v>
+        <v>1.0252205227081859</v>
       </c>
       <c r="N55" s="2">
-        <v>0.0051214057416539838</v>
+        <v>0.0047143871065629117</v>
       </c>
       <c r="O55" s="8" t="b">
         <v>1</v>
@@ -6126,31 +6126,31 @@
         <v>0.75600000000000001</v>
       </c>
       <c r="F56" s="3">
-        <v>0.14050908698443987</v>
+        <v>0.14047717462847501</v>
       </c>
       <c r="G56" s="3">
-        <v>0.1408426237817548</v>
+        <v>0.14081127304765348</v>
       </c>
       <c r="H56" s="2">
-        <v>0.00033353679731493169</v>
+        <v>0.0003340984191784746</v>
       </c>
       <c r="I56" s="4">
-        <v>27.510482527880981</v>
+        <v>27.510722713524615</v>
       </c>
       <c r="J56" s="4">
-        <v>27.511959902742717</v>
+        <v>27.512140565494917</v>
       </c>
       <c r="K56" s="2">
-        <v>0.0014773748617358251</v>
+        <v>0.0014178519703023085</v>
       </c>
       <c r="L56" s="4">
-        <v>1.0148249155562874</v>
+        <v>1.0152091370216123</v>
       </c>
       <c r="M56" s="4">
-        <v>1.0362888065498088</v>
+        <v>1.0363643534883644</v>
       </c>
       <c r="N56" s="2">
-        <v>0.021463890993521417</v>
+        <v>0.021155216466752114</v>
       </c>
       <c r="O56" s="8" t="b">
         <v>1</v>
@@ -6204,31 +6204,31 @@
         <v>0.5</v>
       </c>
       <c r="F57" s="3">
-        <v>0.14401528752568535</v>
+        <v>0.14402275822630178</v>
       </c>
       <c r="G57" s="3">
-        <v>0.13809870236411298</v>
+        <v>0.13810112745155265</v>
       </c>
       <c r="H57" s="2">
-        <v>0.0059165851615723686</v>
+        <v>0.005921630774749137</v>
       </c>
       <c r="I57" s="4">
-        <v>27.510910380474684</v>
+        <v>27.511921907111514</v>
       </c>
       <c r="J57" s="4">
-        <v>27.509726406681068</v>
+        <v>27.510939707918908</v>
       </c>
       <c r="K57" s="2">
-        <v>0.001183973793615678</v>
+        <v>0.00098219919260600363</v>
       </c>
       <c r="L57" s="4">
-        <v>1.0820544695304299</v>
+        <v>1.0818932925629194</v>
       </c>
       <c r="M57" s="4">
-        <v>0.99164031787614226</v>
+        <v>0.99189083146281343</v>
       </c>
       <c r="N57" s="2">
-        <v>0.090414151654287678</v>
+        <v>0.090002461100106013</v>
       </c>
       <c r="O57" s="8" t="b">
         <v>1</v>
@@ -6282,31 +6282,31 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="F58" s="3">
-        <v>0.1410832667405614</v>
+        <v>0.14107017856065204</v>
       </c>
       <c r="G58" s="3">
-        <v>0.14047293140606695</v>
+        <v>0.14046785627830683</v>
       </c>
       <c r="H58" s="2">
-        <v>0.00061033533449444954</v>
+        <v>0.00060232228234521901</v>
       </c>
       <c r="I58" s="4">
-        <v>27.512506880904084</v>
+        <v>27.512311153465134</v>
       </c>
       <c r="J58" s="4">
-        <v>27.51028703541823</v>
+        <v>27.510192998132027</v>
       </c>
       <c r="K58" s="2">
-        <v>0.0022198454858539662</v>
+        <v>0.002118155333107552</v>
       </c>
       <c r="L58" s="4">
-        <v>1.0273864327501268</v>
+        <v>1.0273153312110035</v>
       </c>
       <c r="M58" s="4">
-        <v>1.0275895140347362</v>
+        <v>1.0267615059313759</v>
       </c>
       <c r="N58" s="2">
-        <v>0.00020308128460944097</v>
+        <v>0.00055382527962755113</v>
       </c>
       <c r="O58" s="8" t="b">
         <v>1</v>
@@ -6360,31 +6360,31 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="F59" s="3">
-        <v>0.13862914734298953</v>
+        <v>0.138620096555478</v>
       </c>
       <c r="G59" s="3">
-        <v>0.14268014457133579</v>
+        <v>0.1426448188270463</v>
       </c>
       <c r="H59" s="2">
-        <v>0.0040509972283462592</v>
+        <v>0.004024722271568304</v>
       </c>
       <c r="I59" s="4">
-        <v>27.510762311886026</v>
+        <v>27.510218150172648</v>
       </c>
       <c r="J59" s="4">
-        <v>27.512126988651858</v>
+        <v>27.51207961901622</v>
       </c>
       <c r="K59" s="2">
-        <v>0.0013646767658315184</v>
+        <v>0.0018614688435718563</v>
       </c>
       <c r="L59" s="4">
-        <v>1.0312108212997868</v>
+        <v>1.0309218830808224</v>
       </c>
       <c r="M59" s="4">
-        <v>1.0243511033014749</v>
+        <v>1.0245502450055646</v>
       </c>
       <c r="N59" s="2">
-        <v>0.006859717998311865</v>
+        <v>0.0063716380752578683</v>
       </c>
       <c r="O59" s="8" t="b">
         <v>1</v>
@@ -6438,31 +6438,31 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="F60" s="3">
-        <v>0.13819835518224652</v>
+        <v>0.13820513427498407</v>
       </c>
       <c r="G60" s="3">
-        <v>0.14387749395397831</v>
+        <v>0.14388788630017021</v>
       </c>
       <c r="H60" s="2">
-        <v>0.0056791387717317898</v>
+        <v>0.0056827520251861441</v>
       </c>
       <c r="I60" s="4">
-        <v>27.507886157934934</v>
+        <v>27.506956202863819</v>
       </c>
       <c r="J60" s="4">
-        <v>27.506371660305206</v>
+        <v>27.506110718369143</v>
       </c>
       <c r="K60" s="2">
-        <v>0.0015144976297278845</v>
+        <v>0.00084548449467547471</v>
       </c>
       <c r="L60" s="4">
-        <v>1.0246401809521215</v>
+        <v>1.0248860783652327</v>
       </c>
       <c r="M60" s="4">
-        <v>1.0293352516604937</v>
+        <v>1.0292156541276434</v>
       </c>
       <c r="N60" s="2">
-        <v>0.0046950707083721621</v>
+        <v>0.0043295757624106646</v>
       </c>
       <c r="O60" s="8" t="b">
         <v>1</v>
@@ -6516,31 +6516,31 @@
         <v>-0.074999999999999997</v>
       </c>
       <c r="F61" s="3">
-        <v>0.13968359371386585</v>
+        <v>0.13968946953368663</v>
       </c>
       <c r="G61" s="3">
-        <v>0.14211037404304155</v>
+        <v>0.14211029637499797</v>
       </c>
       <c r="H61" s="2">
-        <v>0.002426780329175704</v>
+        <v>0.002420826841311341</v>
       </c>
       <c r="I61" s="4">
-        <v>27.510883535542177</v>
+        <v>27.510883596547615</v>
       </c>
       <c r="J61" s="4">
-        <v>27.512265459883679</v>
+        <v>27.512322027951029</v>
       </c>
       <c r="K61" s="2">
-        <v>0.0013819243415014171</v>
+        <v>0.0014384314034145973</v>
       </c>
       <c r="L61" s="4">
-        <v>1.0201699148733758</v>
+        <v>1.0197436895334737</v>
       </c>
       <c r="M61" s="4">
-        <v>1.0373502102975718</v>
+        <v>1.0371247984423719</v>
       </c>
       <c r="N61" s="2">
-        <v>0.017180295424195968</v>
+        <v>0.017381108908898213</v>
       </c>
       <c r="O61" s="8" t="b">
         <v>1</v>
@@ -6594,31 +6594,31 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="F62" s="3">
-        <v>0.14033042243817209</v>
+        <v>0.14033158916032773</v>
       </c>
       <c r="G62" s="3">
-        <v>0.14115846369812707</v>
+        <v>0.14115598543888933</v>
       </c>
       <c r="H62" s="2">
-        <v>0.00082804125995497579</v>
+        <v>0.00082439627856159548</v>
       </c>
       <c r="I62" s="4">
-        <v>27.511362128869166</v>
+        <v>27.51262406256069</v>
       </c>
       <c r="J62" s="4">
-        <v>27.50998005820486</v>
+        <v>27.510020308077685</v>
       </c>
       <c r="K62" s="2">
-        <v>0.0013820706643059566</v>
+        <v>0.00260375448300465</v>
       </c>
       <c r="L62" s="4">
-        <v>1.0269021434432677</v>
+        <v>1.0269083764714715</v>
       </c>
       <c r="M62" s="4">
-        <v>1.0303829393450623</v>
+        <v>1.0306763305745854</v>
       </c>
       <c r="N62" s="2">
-        <v>0.00348079590179462</v>
+        <v>0.0037679541031139241</v>
       </c>
       <c r="O62" s="8" t="b">
         <v>1</v>
@@ -6672,31 +6672,31 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F63" s="3">
-        <v>0.15123722170946213</v>
+        <v>0.15124008393665253</v>
       </c>
       <c r="G63" s="3">
-        <v>0.12992018461351812</v>
+        <v>0.1299299827138769</v>
       </c>
       <c r="H63" s="2">
-        <v>0.021317037095944014</v>
+        <v>0.021310101222775629</v>
       </c>
       <c r="I63" s="4">
-        <v>27.518799616578122</v>
+        <v>27.518808551832251</v>
       </c>
       <c r="J63" s="4">
-        <v>27.506800078323238</v>
+        <v>27.506796876724025</v>
       </c>
       <c r="K63" s="2">
-        <v>0.011999538254883646</v>
+        <v>0.012011675108226427</v>
       </c>
       <c r="L63" s="4">
-        <v>1.107419344368983</v>
+        <v>1.1068348335099221</v>
       </c>
       <c r="M63" s="4">
-        <v>0.96007517627794925</v>
+        <v>0.95963549677122062</v>
       </c>
       <c r="N63" s="2">
-        <v>0.14734416809103379</v>
+        <v>0.14719933673870145</v>
       </c>
       <c r="O63" s="8" t="b">
         <v>1</v>
@@ -6750,31 +6750,31 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="F64" s="3">
-        <v>0.13883990155493717</v>
+        <v>0.13881765580826175</v>
       </c>
       <c r="G64" s="3">
-        <v>0.1425896382049934</v>
+        <v>0.14261566409865584</v>
       </c>
       <c r="H64" s="2">
-        <v>0.0037497366500562346</v>
+        <v>0.0037980082903940893</v>
       </c>
       <c r="I64" s="4">
-        <v>27.511060897154948</v>
+        <v>27.511248620915581</v>
       </c>
       <c r="J64" s="4">
-        <v>27.51068792770775</v>
+        <v>27.510491068264059</v>
       </c>
       <c r="K64" s="2">
-        <v>0.00037296944719855674</v>
+        <v>0.00075755265152110951</v>
       </c>
       <c r="L64" s="4">
-        <v>1.0411560581126662</v>
+        <v>1.0412803732148153</v>
       </c>
       <c r="M64" s="4">
-        <v>1.0142561081074659</v>
+        <v>1.01402583449354</v>
       </c>
       <c r="N64" s="2">
-        <v>0.026899950005200291</v>
+        <v>0.027254538721275257</v>
       </c>
       <c r="O64" s="8" t="b">
         <v>1</v>
@@ -6828,31 +6828,31 @@
         <v>0.75600000000000001</v>
       </c>
       <c r="F65" s="3">
-        <v>0.13083067307272422</v>
+        <v>0.13083446162544826</v>
       </c>
       <c r="G65" s="3">
-        <v>0.14838458249548564</v>
+        <v>0.14837856810532762</v>
       </c>
       <c r="H65" s="2">
-        <v>0.017553909422761416</v>
+        <v>0.017544106479879362</v>
       </c>
       <c r="I65" s="4">
-        <v>27.511174257424216</v>
+        <v>27.511196633244936</v>
       </c>
       <c r="J65" s="4">
-        <v>27.510505577784841</v>
+        <v>27.51050904120018</v>
       </c>
       <c r="K65" s="2">
-        <v>0.00066867963937511377</v>
+        <v>0.00068759204475554725</v>
       </c>
       <c r="L65" s="4">
-        <v>1.1020703844036401</v>
+        <v>1.1020403641237981</v>
       </c>
       <c r="M65" s="4">
-        <v>0.97279919995684938</v>
+        <v>0.97276836184078208</v>
       </c>
       <c r="N65" s="2">
-        <v>0.12927118444679075</v>
+        <v>0.12927200228301605</v>
       </c>
       <c r="O65" s="8" t="b">
         <v>1</v>
@@ -6906,31 +6906,31 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F66" s="3">
-        <v>0.13343462424339298</v>
+        <v>0.13343659119197851</v>
       </c>
       <c r="G66" s="3">
-        <v>0.15133231540071998</v>
+        <v>0.15130669829256482</v>
       </c>
       <c r="H66" s="2">
-        <v>0.017897691157327006</v>
+        <v>0.017870107100586313</v>
       </c>
       <c r="I66" s="4">
-        <v>27.509042421481979</v>
+        <v>27.50888201711922</v>
       </c>
       <c r="J66" s="4">
-        <v>27.512868013922116</v>
+        <v>27.5121272385461</v>
       </c>
       <c r="K66" s="2">
-        <v>0.0038255924401369157</v>
+        <v>0.0032452214268801072</v>
       </c>
       <c r="L66" s="4">
-        <v>0.99961665169455327</v>
+        <v>0.99950544316650147</v>
       </c>
       <c r="M66" s="4">
-        <v>1.0715236363325973</v>
+        <v>1.0719292469250339</v>
       </c>
       <c r="N66" s="2">
-        <v>0.071906984638044014</v>
+        <v>0.072423803758532412</v>
       </c>
       <c r="O66" s="8" t="b">
         <v>1</v>
@@ -6984,28 +6984,28 @@
         <v>-0.080000000000000002</v>
       </c>
       <c r="F67" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="G67" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
       </c>
       <c r="I67" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="J67" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="K67" s="2">
         <v>0</v>
       </c>
       <c r="L67" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="M67" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="N67" s="2">
         <v>0</v>
@@ -7062,31 +7062,31 @@
         <v>0.45900000000000002</v>
       </c>
       <c r="F68" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="G68" s="3">
-        <v>0.14072627984857264</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="H68" s="2">
-        <v>1.0534981475823768e-05</v>
+        <v>0</v>
       </c>
       <c r="I68" s="4">
-        <v>27.511393450254957</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="J68" s="4">
-        <v>27.511397910621099</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="K68" s="2">
-        <v>4.4603661422115693e-06</v>
+        <v>0</v>
       </c>
       <c r="L68" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="M68" s="4">
-        <v>1.0274158185617246</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="N68" s="2">
-        <v>0.0001649829569911887</v>
+        <v>0</v>
       </c>
       <c r="O68" s="8" t="b">
         <v>1</v>
@@ -7140,28 +7140,28 @@
         <v>0.215</v>
       </c>
       <c r="F69" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="G69" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
       </c>
       <c r="I69" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="J69" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="K69" s="2">
         <v>0</v>
       </c>
       <c r="L69" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="M69" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="N69" s="2">
         <v>0</v>
@@ -7218,31 +7218,31 @@
         <v>-0.11</v>
       </c>
       <c r="F70" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="G70" s="3">
-        <v>0.14072627984857264</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="H70" s="2">
-        <v>1.0534981475823768e-05</v>
+        <v>0</v>
       </c>
       <c r="I70" s="4">
-        <v>27.511393450254957</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="J70" s="4">
-        <v>27.511397910621099</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="K70" s="2">
-        <v>4.4603661422115693e-06</v>
+        <v>0</v>
       </c>
       <c r="L70" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="M70" s="4">
-        <v>1.0274158185617246</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="N70" s="2">
-        <v>0.0001649829569911887</v>
+        <v>0</v>
       </c>
       <c r="O70" s="8" t="b">
         <v>1</v>
@@ -7296,28 +7296,28 @@
         <v>0.77900000000000003</v>
       </c>
       <c r="F71" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="G71" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
       </c>
       <c r="I71" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="J71" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="K71" s="2">
         <v>0</v>
       </c>
       <c r="L71" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="M71" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="N71" s="2">
         <v>0</v>
@@ -7374,31 +7374,31 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="F72" s="3">
-        <v>0.14072627984857264</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="G72" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="H72" s="2">
-        <v>1.0534981475823768e-05</v>
+        <v>0</v>
       </c>
       <c r="I72" s="4">
-        <v>27.511397910621099</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="J72" s="4">
-        <v>27.511393450254957</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="K72" s="2">
-        <v>4.4603661422115693e-06</v>
+        <v>0</v>
       </c>
       <c r="L72" s="4">
-        <v>1.0274158185617246</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="M72" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="N72" s="2">
-        <v>0.0001649829569911887</v>
+        <v>0</v>
       </c>
       <c r="O72" s="8" t="b">
         <v>1</v>
@@ -7452,31 +7452,31 @@
         <v>-0.0038700000000000002</v>
       </c>
       <c r="F73" s="3">
-        <v>0.14038123709205486</v>
+        <v>0.1403787110975275</v>
       </c>
       <c r="G73" s="3">
-        <v>0.14174180377019235</v>
+        <v>0.14170939214513248</v>
       </c>
       <c r="H73" s="2">
-        <v>0.0013605666781374981</v>
+        <v>0.0013306810476049757</v>
       </c>
       <c r="I73" s="4">
-        <v>27.511562489032826</v>
+        <v>27.510726188523506</v>
       </c>
       <c r="J73" s="4">
-        <v>27.510421893656599</v>
+        <v>27.510389928006191</v>
       </c>
       <c r="K73" s="2">
-        <v>0.0011405953762277932</v>
+        <v>0.00033626051731516782</v>
       </c>
       <c r="L73" s="4">
-        <v>1.031066820962858</v>
+        <v>1.0313460114991622</v>
       </c>
       <c r="M73" s="4">
-        <v>1.0171536285781329</v>
+        <v>1.0171553252501151</v>
       </c>
       <c r="N73" s="2">
-        <v>0.013913192384725104</v>
+        <v>0.014190686249047069</v>
       </c>
       <c r="O73" s="8" t="b">
         <v>1</v>
@@ -7530,31 +7530,31 @@
         <v>0.54195000000000004</v>
       </c>
       <c r="F74" s="3">
-        <v>0.14245493226669509</v>
+        <v>0.14245996793949064</v>
       </c>
       <c r="G74" s="3">
-        <v>0.13877619175318515</v>
+        <v>0.13878258097510124</v>
       </c>
       <c r="H74" s="2">
-        <v>0.0036787405135099427</v>
+        <v>0.0036773869643894064</v>
       </c>
       <c r="I74" s="4">
-        <v>27.510988292590412</v>
+        <v>27.510223028851669</v>
       </c>
       <c r="J74" s="4">
-        <v>27.51111092268701</v>
+        <v>27.511889686003826</v>
       </c>
       <c r="K74" s="2">
-        <v>0.00012263009659818636</v>
+        <v>0.0016666571521568585</v>
       </c>
       <c r="L74" s="4">
-        <v>1.0073050999227979</v>
+        <v>1.0074551352972647</v>
       </c>
       <c r="M74" s="4">
-        <v>1.04886638215211</v>
+        <v>1.0489058144435035</v>
       </c>
       <c r="N74" s="2">
-        <v>0.041561282229312102</v>
+        <v>0.041450679146238789</v>
       </c>
       <c r="O74" s="8" t="b">
         <v>1</v>
@@ -7608,31 +7608,31 @@
         <v>0.57286000000000004</v>
       </c>
       <c r="F75" s="3">
-        <v>0.14234834552845405</v>
+        <v>0.1423487405747689</v>
       </c>
       <c r="G75" s="3">
-        <v>0.13958562211606715</v>
+        <v>0.13958517616408975</v>
       </c>
       <c r="H75" s="2">
-        <v>0.0027627234123868971</v>
+        <v>0.0027635644106791535</v>
       </c>
       <c r="I75" s="4">
-        <v>27.510677954774792</v>
+        <v>27.510680173768265</v>
       </c>
       <c r="J75" s="4">
-        <v>27.511583912294043</v>
+        <v>27.511585530860259</v>
       </c>
       <c r="K75" s="2">
-        <v>0.00090595751925093282</v>
+        <v>0.00090535709199457415</v>
       </c>
       <c r="L75" s="4">
-        <v>1.0090042600044988</v>
+        <v>1.009175833815708</v>
       </c>
       <c r="M75" s="4">
-        <v>1.0405810818441068</v>
+        <v>1.0405378231917901</v>
       </c>
       <c r="N75" s="2">
-        <v>0.031576821839607971</v>
+        <v>0.031361989376082144</v>
       </c>
       <c r="O75" s="8" t="b">
         <v>1</v>
@@ -7686,31 +7686,31 @@
         <v>-0.023587</v>
       </c>
       <c r="F76" s="3">
-        <v>0.14109287310694493</v>
+        <v>0.1410954120468228</v>
       </c>
       <c r="G76" s="3">
-        <v>0.14060307889289858</v>
+        <v>0.14057805389578398</v>
       </c>
       <c r="H76" s="2">
-        <v>0.00048979421404635182</v>
+        <v>0.00051735815103881588</v>
       </c>
       <c r="I76" s="4">
-        <v>27.512273194972409</v>
+        <v>27.510945389747974</v>
       </c>
       <c r="J76" s="4">
-        <v>27.511499519639756</v>
+        <v>27.511559403725869</v>
       </c>
       <c r="K76" s="2">
-        <v>0.00077367533265260136</v>
+        <v>0.00061401397789495604</v>
       </c>
       <c r="L76" s="4">
-        <v>1.0236979984790045</v>
+        <v>1.023540280248826</v>
       </c>
       <c r="M76" s="4">
-        <v>1.0284841665616278</v>
+        <v>1.027967551629682</v>
       </c>
       <c r="N76" s="2">
-        <v>0.0047861680826233322</v>
+        <v>0.0044272713808559683</v>
       </c>
       <c r="O76" s="8" t="b">
         <v>1</v>
@@ -7764,31 +7764,31 @@
         <v>0.746</v>
       </c>
       <c r="F77" s="3">
-        <v>0.14214275790674807</v>
+        <v>0.14212466396035714</v>
       </c>
       <c r="G77" s="3">
-        <v>0.13950811377398475</v>
+        <v>0.13950175823112029</v>
       </c>
       <c r="H77" s="2">
-        <v>0.0026346441327633197</v>
+        <v>0.0026229057292368463</v>
       </c>
       <c r="I77" s="4">
-        <v>27.511354260745634</v>
+        <v>27.511382524805015</v>
       </c>
       <c r="J77" s="4">
-        <v>27.511725944248951</v>
+        <v>27.511621700205353</v>
       </c>
       <c r="K77" s="2">
-        <v>0.0003716835033173993</v>
+        <v>0.00023917540033835394</v>
       </c>
       <c r="L77" s="4">
-        <v>1.0119084814396264</v>
+        <v>1.0122585672061366</v>
       </c>
       <c r="M77" s="4">
-        <v>1.040445291439837</v>
+        <v>1.0403032072069676</v>
       </c>
       <c r="N77" s="2">
-        <v>0.028536810000210577</v>
+        <v>0.028044640000830956</v>
       </c>
       <c r="O77" s="8" t="b">
         <v>1</v>
@@ -7842,31 +7842,31 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="F78" s="3">
-        <v>0.14128655124439141</v>
+        <v>0.14130300881323521</v>
       </c>
       <c r="G78" s="3">
-        <v>0.14005368050573549</v>
+        <v>0.1400631867344741</v>
       </c>
       <c r="H78" s="2">
-        <v>0.0012328707386559112</v>
+        <v>0.0012398220787611103</v>
       </c>
       <c r="I78" s="4">
-        <v>27.51146407245858</v>
+        <v>27.510651448034309</v>
       </c>
       <c r="J78" s="4">
-        <v>27.5110307102305</v>
+        <v>27.51151341536081</v>
       </c>
       <c r="K78" s="2">
-        <v>0.00043336222807965896</v>
+        <v>0.00086196732650023478</v>
       </c>
       <c r="L78" s="4">
-        <v>1.0203732567774515</v>
+        <v>1.0206232331514817</v>
       </c>
       <c r="M78" s="4">
-        <v>1.034651422656717</v>
+        <v>1.0353546444549515</v>
       </c>
       <c r="N78" s="2">
-        <v>0.014278165879265448</v>
+        <v>0.014731411303469777</v>
       </c>
       <c r="O78" s="8" t="b">
         <v>1</v>
@@ -7920,31 +7920,31 @@
         <v>0.02</v>
       </c>
       <c r="F79" s="3">
-        <v>0.14074141119587835</v>
+        <v>0.14073997053067733</v>
       </c>
       <c r="G79" s="3">
-        <v>0.14072690518552586</v>
+        <v>0.14072951571033551</v>
       </c>
       <c r="H79" s="2">
-        <v>1.4506010352494103e-05</v>
+        <v>1.045482034181533e-05</v>
       </c>
       <c r="I79" s="4">
-        <v>27.511466276638203</v>
+        <v>27.510631348154789</v>
       </c>
       <c r="J79" s="4">
-        <v>27.511319504369567</v>
+        <v>27.510491391357959</v>
       </c>
       <c r="K79" s="2">
-        <v>0.00014677226863568649</v>
+        <v>0.00013995679682921036</v>
       </c>
       <c r="L79" s="4">
-        <v>1.0268165907815647</v>
+        <v>1.0275313042235843</v>
       </c>
       <c r="M79" s="4">
-        <v>1.0275136392284456</v>
+        <v>1.0268954055775506</v>
       </c>
       <c r="N79" s="2">
-        <v>0.00069704844688089907</v>
+        <v>0.00063589864603375013</v>
       </c>
       <c r="O79" s="8" t="b">
         <v>1</v>
@@ -7998,31 +7998,31 @@
         <v>0.76000000000000001</v>
       </c>
       <c r="F80" s="3">
-        <v>0.14073245917566454</v>
+        <v>0.14072435380613527</v>
       </c>
       <c r="G80" s="3">
-        <v>0.14073348410850908</v>
+        <v>0.14072613982679527</v>
       </c>
       <c r="H80" s="2">
-        <v>1.0249328445399719e-06</v>
+        <v>1.7860206600051054e-06</v>
       </c>
       <c r="I80" s="4">
-        <v>27.510590623865767</v>
+        <v>27.510597094636125</v>
       </c>
       <c r="J80" s="4">
-        <v>27.511371412318056</v>
+        <v>27.511388230203011</v>
       </c>
       <c r="K80" s="2">
-        <v>0.00078078845228901628</v>
+        <v>0.00079113556688525932</v>
       </c>
       <c r="L80" s="4">
-        <v>1.0269164559272082</v>
+        <v>1.0265008595449419</v>
       </c>
       <c r="M80" s="4">
-        <v>1.0273933385240866</v>
+        <v>1.0275347815415146</v>
       </c>
       <c r="N80" s="2">
-        <v>0.00047688259687839185</v>
+        <v>0.0010339219965727064</v>
       </c>
       <c r="O80" s="8" t="b">
         <v>1</v>
@@ -8076,31 +8076,31 @@
         <v>0.34999999999999998</v>
       </c>
       <c r="F81" s="3">
-        <v>0.14070555878929239</v>
+        <v>0.14070196818340805</v>
       </c>
       <c r="G81" s="3">
-        <v>0.14075404809781861</v>
+        <v>0.14075940083266564</v>
       </c>
       <c r="H81" s="2">
-        <v>4.8489308526217245e-05</v>
+        <v>5.7432649257588286e-05</v>
       </c>
       <c r="I81" s="4">
-        <v>27.510875849877436</v>
+        <v>27.511446870817224</v>
       </c>
       <c r="J81" s="4">
-        <v>27.511655055561562</v>
+        <v>27.511311965764946</v>
       </c>
       <c r="K81" s="2">
-        <v>0.0007792056841253725</v>
+        <v>0.00013490505227764515</v>
       </c>
       <c r="L81" s="4">
-        <v>1.0273949838039909</v>
+        <v>1.0273308568399584</v>
       </c>
       <c r="M81" s="4">
-        <v>1.0272483923011233</v>
+        <v>1.02754002495074</v>
       </c>
       <c r="N81" s="2">
-        <v>0.00014659150286755462</v>
+        <v>0.00020916811078164343</v>
       </c>
       <c r="O81" s="8" t="b">
         <v>1</v>
@@ -8154,31 +8154,31 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="F82" s="3">
-        <v>0.1425781307089414</v>
+        <v>0.14258371961622654</v>
       </c>
       <c r="G82" s="3">
-        <v>0.13886283276341999</v>
+        <v>0.1388828486216421</v>
       </c>
       <c r="H82" s="2">
-        <v>0.0037152979455214175</v>
+        <v>0.0037008709945844376</v>
       </c>
       <c r="I82" s="4">
-        <v>27.502424768814137</v>
+        <v>27.502791401286913</v>
       </c>
       <c r="J82" s="4">
-        <v>27.519438059654647</v>
+        <v>27.519908402700764</v>
       </c>
       <c r="K82" s="2">
-        <v>0.017013290840509399</v>
+        <v>0.017117001413851085</v>
       </c>
       <c r="L82" s="4">
-        <v>1.03131093071623</v>
+        <v>1.0310769856064599</v>
       </c>
       <c r="M82" s="4">
-        <v>1.0224649453142305</v>
+        <v>1.0225191617576819</v>
       </c>
       <c r="N82" s="2">
-        <v>0.0088459854019995454</v>
+        <v>0.0085578238487780123</v>
       </c>
       <c r="O82" s="8" t="b">
         <v>1</v>
@@ -8232,31 +8232,31 @@
         <v>0.83750000000000002</v>
       </c>
       <c r="F83" s="3">
-        <v>0.14819321349364337</v>
+        <v>0.14819300331935081</v>
       </c>
       <c r="G83" s="3">
-        <v>0.13416074779839651</v>
+        <v>0.13415346028586633</v>
       </c>
       <c r="H83" s="2">
-        <v>0.014032465695246854</v>
+        <v>0.014039543033484481</v>
       </c>
       <c r="I83" s="4">
-        <v>27.510723800845369</v>
+        <v>27.510543117022848</v>
       </c>
       <c r="J83" s="4">
-        <v>27.511232100599102</v>
+        <v>27.510685609228915</v>
       </c>
       <c r="K83" s="2">
-        <v>0.00050829975373289926</v>
+        <v>0.00014249220606643576</v>
       </c>
       <c r="L83" s="4">
-        <v>1.0202972122285416</v>
+        <v>1.0203053692060571</v>
       </c>
       <c r="M83" s="4">
-        <v>1.0331539723831298</v>
+        <v>1.0329090219199384</v>
       </c>
       <c r="N83" s="2">
-        <v>0.012856760154588143</v>
+        <v>0.012603652713881308</v>
       </c>
       <c r="O83" s="8" t="b">
         <v>1</v>
@@ -8310,31 +8310,31 @@
         <v>0.38</v>
       </c>
       <c r="F84" s="3">
-        <v>0.14547347993185411</v>
+        <v>0.14546646735415925</v>
       </c>
       <c r="G84" s="3">
-        <v>0.13611690028373916</v>
+        <v>0.13608070322990196</v>
       </c>
       <c r="H84" s="2">
-        <v>0.0093565796481149544</v>
+        <v>0.0093857641242572898</v>
       </c>
       <c r="I84" s="4">
-        <v>27.513590804180581</v>
+        <v>27.51359075208336</v>
       </c>
       <c r="J84" s="4">
-        <v>27.521402732450838</v>
+        <v>27.521435514029122</v>
       </c>
       <c r="K84" s="2">
-        <v>0.0078119282702573401</v>
+        <v>0.0078447619457620021</v>
       </c>
       <c r="L84" s="4">
-        <v>1.0157766592961586</v>
+        <v>1.0157637259109398</v>
       </c>
       <c r="M84" s="4">
-        <v>1.037995257540274</v>
+        <v>1.0372207213462801</v>
       </c>
       <c r="N84" s="2">
-        <v>0.022218598244115428</v>
+        <v>0.021456995435340298</v>
       </c>
       <c r="O84" s="8" t="b">
         <v>1</v>
@@ -8388,31 +8388,31 @@
         <v>0.34999999999999998</v>
       </c>
       <c r="F85" s="3">
-        <v>0.12552786496926327</v>
+        <v>0.12554583247888698</v>
       </c>
       <c r="G85" s="3">
-        <v>0.15187483410319041</v>
+        <v>0.15186025672882186</v>
       </c>
       <c r="H85" s="2">
-        <v>0.026346969133927145</v>
+        <v>0.026314424249934881</v>
       </c>
       <c r="I85" s="4">
-        <v>27.511012751647058</v>
+        <v>27.511591327671113</v>
       </c>
       <c r="J85" s="4">
-        <v>27.510604394039035</v>
+        <v>27.51134928896164</v>
       </c>
       <c r="K85" s="2">
-        <v>0.00040835760802337973</v>
+        <v>0.00024203870947303585</v>
       </c>
       <c r="L85" s="4">
-        <v>1.1034788368319166</v>
+        <v>1.1034775249506017</v>
       </c>
       <c r="M85" s="4">
-        <v>0.98258869101576674</v>
+        <v>0.98268536957054542</v>
       </c>
       <c r="N85" s="2">
-        <v>0.12089014581614987</v>
+        <v>0.12079215538005628</v>
       </c>
       <c r="O85" s="8" t="b">
         <v>1</v>
@@ -8466,31 +8466,31 @@
         <v>0.63</v>
       </c>
       <c r="F86" s="3">
-        <v>0.14072663622323101</v>
+        <v>0.14071490350558397</v>
       </c>
       <c r="G86" s="3">
-        <v>0.14071422807311085</v>
+        <v>0.14072154332977197</v>
       </c>
       <c r="H86" s="2">
-        <v>1.2408150120157835e-05</v>
+        <v>6.6398241879983555e-06</v>
       </c>
       <c r="I86" s="4">
-        <v>27.511404141952767</v>
+        <v>27.511389710163542</v>
       </c>
       <c r="J86" s="4">
-        <v>27.510806116311301</v>
+        <v>27.510595339723636</v>
       </c>
       <c r="K86" s="2">
-        <v>0.00059802564146593795</v>
+        <v>0.00079437043990537859</v>
       </c>
       <c r="L86" s="4">
-        <v>1.0275837042690799</v>
+        <v>1.0272680813892325</v>
       </c>
       <c r="M86" s="4">
-        <v>1.0276130596207806</v>
+        <v>1.027677015482988</v>
       </c>
       <c r="N86" s="2">
-        <v>2.935535170078829e-05</v>
+        <v>0.00040893409375541978</v>
       </c>
       <c r="O86" s="8" t="b">
         <v>1</v>
@@ -8544,31 +8544,31 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="F87" s="3">
-        <v>0.14004793539386212</v>
+        <v>0.14004544926731921</v>
       </c>
       <c r="G87" s="3">
-        <v>0.14139079768816568</v>
+        <v>0.14139821302980629</v>
       </c>
       <c r="H87" s="2">
-        <v>0.001342862294303554</v>
+        <v>0.0013527637624870803</v>
       </c>
       <c r="I87" s="4">
-        <v>27.510806914148986</v>
+        <v>27.510707195916098</v>
       </c>
       <c r="J87" s="4">
-        <v>27.511451564091374</v>
+        <v>27.510955084022555</v>
       </c>
       <c r="K87" s="2">
-        <v>0.00064464994238733198</v>
+        <v>0.0002478881064575944</v>
       </c>
       <c r="L87" s="4">
-        <v>1.0307350885318791</v>
+        <v>1.0303701151085727</v>
       </c>
       <c r="M87" s="4">
-        <v>1.0246184679003862</v>
+        <v>1.0244176261436406</v>
       </c>
       <c r="N87" s="2">
-        <v>0.0061166206314928751</v>
+        <v>0.0059524889649320567</v>
       </c>
       <c r="O87" s="8" t="b">
         <v>1</v>
@@ -8622,31 +8622,31 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="F88" s="3">
-        <v>0.15182165746227563</v>
+        <v>0.15184337528107494</v>
       </c>
       <c r="G88" s="3">
-        <v>0.12559216721718552</v>
+        <v>0.12560346420091817</v>
       </c>
       <c r="H88" s="2">
-        <v>0.026229490245090109</v>
+        <v>0.026239911080156775</v>
       </c>
       <c r="I88" s="4">
-        <v>27.511375653759615</v>
+        <v>27.511365722686776</v>
       </c>
       <c r="J88" s="4">
-        <v>27.510433922562868</v>
+        <v>27.511067395881639</v>
       </c>
       <c r="K88" s="2">
-        <v>0.00094173119674678674</v>
+        <v>0.00029832680513663945</v>
       </c>
       <c r="L88" s="4">
-        <v>0.98419537488951347</v>
+        <v>0.9838430416733106</v>
       </c>
       <c r="M88" s="4">
-        <v>1.1035102483261234</v>
+        <v>1.1034057726619417</v>
       </c>
       <c r="N88" s="2">
-        <v>0.11931487343660996</v>
+        <v>0.11956273098863113</v>
       </c>
       <c r="O88" s="8" t="b">
         <v>1</v>
@@ -8700,31 +8700,31 @@
         <v>0.65000000000000002</v>
       </c>
       <c r="F89" s="3">
-        <v>0.15180870916996656</v>
+        <v>0.15181957555043926</v>
       </c>
       <c r="G89" s="3">
-        <v>0.13055212962945525</v>
+        <v>0.13052091230339868</v>
       </c>
       <c r="H89" s="2">
-        <v>0.0212565795405113</v>
+        <v>0.021298663247040578</v>
       </c>
       <c r="I89" s="4">
-        <v>27.510654309329368</v>
+        <v>27.510927882267708</v>
       </c>
       <c r="J89" s="4">
-        <v>27.510848075354261</v>
+        <v>27.511307811421489</v>
       </c>
       <c r="K89" s="2">
-        <v>0.00019376602489273864</v>
+        <v>0.00037992915378026737</v>
       </c>
       <c r="L89" s="4">
-        <v>0.98284570357107537</v>
+        <v>0.98348625010143254</v>
       </c>
       <c r="M89" s="4">
-        <v>1.0757255030073491</v>
+        <v>1.076234188999853</v>
       </c>
       <c r="N89" s="2">
-        <v>0.09287979943627378</v>
+        <v>0.092747938898420479</v>
       </c>
       <c r="O89" s="8" t="b">
         <v>1</v>
@@ -8778,31 +8778,31 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="F90" s="3">
-        <v>0.14184108164606812</v>
+        <v>0.14184553169861397</v>
       </c>
       <c r="G90" s="3">
-        <v>0.13960515054013026</v>
+        <v>0.13959813239403102</v>
       </c>
       <c r="H90" s="2">
-        <v>0.0022359311059378662</v>
+        <v>0.0022473993045829532</v>
       </c>
       <c r="I90" s="4">
-        <v>27.510537653468134</v>
+        <v>27.510825744029319</v>
       </c>
       <c r="J90" s="4">
-        <v>27.512286862824624</v>
+        <v>27.510802461109051</v>
       </c>
       <c r="K90" s="2">
-        <v>0.0017492093564897004</v>
+        <v>2.3282920267320151e-05</v>
       </c>
       <c r="L90" s="4">
-        <v>1.0227247869708487</v>
+        <v>1.0224401914687291</v>
       </c>
       <c r="M90" s="4">
-        <v>1.0325175813702339</v>
+        <v>1.0320137016507456</v>
       </c>
       <c r="N90" s="2">
-        <v>0.0097927943993851852</v>
+        <v>0.0095735101820164648</v>
       </c>
       <c r="O90" s="8" t="b">
         <v>1</v>
@@ -8856,31 +8856,31 @@
         <v>7600</v>
       </c>
       <c r="F91" s="3">
-        <v>0.14123439355133297</v>
+        <v>0.14123088344720902</v>
       </c>
       <c r="G91" s="3">
-        <v>0.13995614196132475</v>
+        <v>0.14000130591068613</v>
       </c>
       <c r="H91" s="2">
-        <v>0.001278251590008217</v>
+        <v>0.0012295775365228911</v>
       </c>
       <c r="I91" s="4">
-        <v>27.510818185233745</v>
+        <v>27.51139508055121</v>
       </c>
       <c r="J91" s="4">
-        <v>27.511349183075367</v>
+        <v>27.511498501797632</v>
       </c>
       <c r="K91" s="2">
-        <v>0.00053099784162213837</v>
+        <v>0.00010342124642193085</v>
       </c>
       <c r="L91" s="4">
-        <v>1.0060386936486096</v>
+        <v>1.0060394740276812</v>
       </c>
       <c r="M91" s="4">
-        <v>1.0854688315615693</v>
+        <v>1.085426410881474</v>
       </c>
       <c r="N91" s="2">
-        <v>0.079430137912959609</v>
+        <v>0.079386936853792722</v>
       </c>
       <c r="O91" s="8" t="b">
         <v>1</v>
@@ -8934,31 +8934,31 @@
         <v>-0.085000000000000006</v>
       </c>
       <c r="F92" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="G92" s="3">
-        <v>0.14072627984857264</v>
+        <v>0.14073702286229747</v>
       </c>
       <c r="H92" s="2">
-        <v>1.0534981475823768e-05</v>
+        <v>0</v>
       </c>
       <c r="I92" s="4">
-        <v>27.511393450254957</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="J92" s="4">
-        <v>27.511397910621099</v>
+        <v>27.510202261112909</v>
       </c>
       <c r="K92" s="2">
-        <v>4.4603661422115693e-06</v>
+        <v>0</v>
       </c>
       <c r="L92" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="M92" s="4">
-        <v>1.0274158185617246</v>
+        <v>1.0273204438213062</v>
       </c>
       <c r="N92" s="2">
-        <v>0.0001649829569911887</v>
+        <v>0</v>
       </c>
       <c r="O92" s="8" t="b">
         <v>1</v>
@@ -9012,28 +9012,28 @@
         <v>0.065000000000000002</v>
       </c>
       <c r="F93" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="G93" s="3">
-        <v>0.14071574486709682</v>
+        <v>0.14070760141879987</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
       </c>
       <c r="I93" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="J93" s="4">
-        <v>27.511393450254957</v>
+        <v>27.511390446925816</v>
       </c>
       <c r="K93" s="2">
         <v>0</v>
       </c>
       <c r="L93" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="M93" s="4">
-        <v>1.0272508356047334</v>
+        <v>1.0265631400907453</v>
       </c>
       <c r="N93" s="2">
         <v>0</v>
@@ -9090,31 +9090,31 @@
         <v>58000</v>
       </c>
       <c r="F94" s="3">
-        <v>0.14189188149003992</v>
+        <v>0.14192058580744207</v>
       </c>
       <c r="G94" s="3">
-        <v>0.13921861854170367</v>
+        <v>0.13922372149338361</v>
       </c>
       <c r="H94" s="2">
-        <v>0.0026732629483362525</v>
+        <v>0.0026968643140584669</v>
       </c>
       <c r="I94" s="4">
-        <v>27.511511045976761</v>
+        <v>27.510663102665546</v>
       </c>
       <c r="J94" s="4">
-        <v>27.509882617402411</v>
+        <v>27.510044679660553</v>
       </c>
       <c r="K94" s="2">
-        <v>0.0016284285743495275</v>
+        <v>0.00061842300499392877</v>
       </c>
       <c r="L94" s="4">
-        <v>1.0297636597031901</v>
+        <v>1.0294829127726559</v>
       </c>
       <c r="M94" s="4">
-        <v>1.0308099213875723</v>
+        <v>1.0311299053071026</v>
       </c>
       <c r="N94" s="2">
-        <v>0.0010462616843822659</v>
+        <v>0.0016469925344466674</v>
       </c>
       <c r="O94" s="8" t="b">
         <v>1</v>
@@ -9168,31 +9168,31 @@
         <v>60</v>
       </c>
       <c r="F95" s="3">
-        <v>0.14743761976100367</v>
+        <v>0.14746053946631393</v>
       </c>
       <c r="G95" s="3">
-        <v>0.13497913969654107</v>
+        <v>0.13497111562643793</v>
       </c>
       <c r="H95" s="2">
-        <v>0.012458480064462596</v>
+        <v>0.012489423839876002</v>
       </c>
       <c r="I95" s="4">
-        <v>27.511372545952668</v>
+        <v>27.510938660489785</v>
       </c>
       <c r="J95" s="4">
-        <v>27.512211856389683</v>
+        <v>27.511399296071659</v>
       </c>
       <c r="K95" s="2">
-        <v>0.00083931043701568342</v>
+        <v>0.0004606355818737029</v>
       </c>
       <c r="L95" s="4">
-        <v>1.0001286533324085</v>
+        <v>1.0001287870202602</v>
       </c>
       <c r="M95" s="4">
-        <v>1.0540507156076111</v>
+        <v>1.0540378834010624</v>
       </c>
       <c r="N95" s="2">
-        <v>0.053922062275202576</v>
+        <v>0.053909096380802213</v>
       </c>
       <c r="O95" s="8" t="b">
         <v>1</v>
